--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2893,10 +2893,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131889571</v>
+        <v>131888320</v>
       </c>
       <c r="B19" t="n">
-        <v>83110</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497567</v>
+        <v>497822</v>
       </c>
       <c r="R19" t="n">
-        <v>7040434</v>
+        <v>7040565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,6 +2969,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på både döda och levande granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2984,11 +2989,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2999,9 +2999,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3019,10 +3024,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131888320</v>
+        <v>131889571</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>83110</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3030,21 +3035,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497822</v>
+        <v>497567</v>
       </c>
       <c r="R20" t="n">
-        <v>7040565</v>
+        <v>7040434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,11 +3100,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på både döda och levande granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3115,6 +3115,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3125,14 +3130,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -7078,10 +7078,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131888306</v>
+        <v>131889565</v>
       </c>
       <c r="B51" t="n">
-        <v>91852</v>
+        <v>79264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7089,26 +7089,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497599</v>
+        <v>497779</v>
       </c>
       <c r="R51" t="n">
-        <v>7040426</v>
+        <v>7040469</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Fruktkroppar i en stående död gran med full längd och 40 cm i brösthöjdsdiameter. I grannaturskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7189,14 +7189,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7214,10 +7209,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131889565</v>
+        <v>131888306</v>
       </c>
       <c r="B52" t="n">
-        <v>79264</v>
+        <v>91852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7225,26 +7220,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7252,10 +7247,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497779</v>
+        <v>497599</v>
       </c>
       <c r="R52" t="n">
-        <v>7040469</v>
+        <v>7040426</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7292,7 +7287,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fruktkroppar i en stående död gran med full längd och 40 cm i brösthöjdsdiameter. I grannaturskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7325,9 +7320,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889526</v>
+        <v>131889849</v>
       </c>
       <c r="B53" t="n">
-        <v>83244</v>
+        <v>91852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7356,26 +7356,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497605</v>
+        <v>497679</v>
       </c>
       <c r="R53" t="n">
-        <v>7040259</v>
+        <v>7040341</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7471,10 +7471,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889543</v>
+        <v>131889848</v>
       </c>
       <c r="B54" t="n">
-        <v>78276</v>
+        <v>91852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7482,26 +7482,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497577</v>
+        <v>497679</v>
       </c>
       <c r="R54" t="n">
-        <v>7040217</v>
+        <v>7040355</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7597,10 +7597,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131889531</v>
+        <v>131889851</v>
       </c>
       <c r="B55" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7608,23 +7608,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
@@ -7639,10 +7635,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497831</v>
+        <v>497564</v>
       </c>
       <c r="R55" t="n">
-        <v>7040503</v>
+        <v>7040145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7692,11 +7688,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ55" t="inlineStr">
         <is>
           <t>gran</t>
@@ -7707,14 +7698,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7732,41 +7718,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131889528</v>
+        <v>131889865</v>
       </c>
       <c r="B56" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7774,10 +7756,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497610</v>
+        <v>497474</v>
       </c>
       <c r="R56" t="n">
-        <v>7040287</v>
+        <v>7040328</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7812,6 +7794,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mycket rikligt med garnlav här!!</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7829,7 +7816,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7842,14 +7829,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7867,10 +7849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889534</v>
+        <v>131889775</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>83244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7878,30 +7860,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7909,10 +7887,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497640</v>
+        <v>497671</v>
       </c>
       <c r="R57" t="n">
-        <v>7040232</v>
+        <v>7040587</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7960,6 +7938,11 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -7992,10 +7975,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131889532</v>
+        <v>131889883</v>
       </c>
       <c r="B58" t="n">
-        <v>91832</v>
+        <v>83236</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8003,30 +7986,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8034,10 +8013,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497828</v>
+        <v>497621</v>
       </c>
       <c r="R58" t="n">
-        <v>7040485</v>
+        <v>7040366</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8087,24 +8066,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8122,10 +8086,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889540</v>
+        <v>131889526</v>
       </c>
       <c r="B59" t="n">
-        <v>92131</v>
+        <v>83244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8133,30 +8097,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8164,10 +8124,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497796</v>
+        <v>497605</v>
       </c>
       <c r="R59" t="n">
-        <v>7040452</v>
+        <v>7040259</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8232,14 +8192,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8257,10 +8212,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889533</v>
+        <v>131889543</v>
       </c>
       <c r="B60" t="n">
-        <v>91832</v>
+        <v>78276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8268,30 +8223,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8299,10 +8250,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497784</v>
+        <v>497577</v>
       </c>
       <c r="R60" t="n">
-        <v>7040452</v>
+        <v>7040217</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8352,6 +8303,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ60" t="inlineStr">
         <is>
           <t>gran</t>
@@ -8362,14 +8318,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8387,10 +8338,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889542</v>
+        <v>131889808</v>
       </c>
       <c r="B61" t="n">
-        <v>78276</v>
+        <v>57902</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8398,26 +8349,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8425,10 +8381,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497686</v>
+        <v>497512</v>
       </c>
       <c r="R61" t="n">
-        <v>7040411</v>
+        <v>7040418</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8463,13 +8419,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8478,6 +8438,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ61" t="inlineStr">
         <is>
           <t>gran</t>
@@ -8488,9 +8453,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8508,37 +8478,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889525</v>
+        <v>131889796</v>
       </c>
       <c r="B62" t="n">
-        <v>83244</v>
+        <v>92555</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8546,10 +8520,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497570</v>
+        <v>497619</v>
       </c>
       <c r="R62" t="n">
-        <v>7040437</v>
+        <v>7040378</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8634,39 +8608,40 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131889527</v>
+        <v>131889807</v>
       </c>
       <c r="B63" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8676,10 +8651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497740</v>
+        <v>497520</v>
       </c>
       <c r="R63" t="n">
-        <v>7040504</v>
+        <v>7040421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8714,13 +8689,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8729,6 +8708,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ63" t="inlineStr">
         <is>
           <t>gran</t>
@@ -8739,14 +8723,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8761,6 +8740,7777 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131889776</v>
+      </c>
+      <c r="B64" t="n">
+        <v>83244</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>497530</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7040312</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131889829</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78276</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>497561</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7040467</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131889816</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>497433</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7040274</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131889855</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>497671</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7040299</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131889878</v>
+      </c>
+      <c r="B68" t="n">
+        <v>83110</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>497559</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7040336</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131889809</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>497622</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7040347</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131889804</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>497834</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7040513</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131889531</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>497831</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7040503</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131889834</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>497411</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7040245</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131889528</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>497610</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7040287</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131889534</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>497640</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7040232</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131889810</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>497721</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7040314</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131889785</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>497617</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7040562</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131889783</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>497799</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7040466</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131889863</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>497565</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7040468</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131889869</v>
+      </c>
+      <c r="B79" t="n">
+        <v>83110</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>497732</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7040316</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131889847</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>497569</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7040368</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131889838</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>497570</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7040146</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131889831</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>497699</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7040333</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131889789</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>497816</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7040474</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131889866</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>497516</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7040148</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt!!</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131889532</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>497828</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7040485</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131889540</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92131</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>658</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>497796</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7040452</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131889818</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>497444</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7040224</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>131889811</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>497625</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7040291</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131889815</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>497472</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7040345</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131889795</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92555</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>497767</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7040478</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>131889880</v>
+      </c>
+      <c r="B91" t="n">
+        <v>89217</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>510</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>497791</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7040457</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>131889868</v>
+      </c>
+      <c r="B92" t="n">
+        <v>83110</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>497696</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7040335</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>131889533</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>497784</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7040452</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>131889823</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57743</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>497598</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7040321</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>131889835</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>497549</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7040130</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>131889853</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>497592</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7040180</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>131889786</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>497661</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7040289</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>131889805</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>497802</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7040466</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>131889806</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>497569</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7040455</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>131889819</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>497516</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7040136</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>131889852</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>497574</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7040148</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>131889881</v>
+      </c>
+      <c r="B102" t="n">
+        <v>83236</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>308</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>497527</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7040360</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>131889542</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78276</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>497686</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7040411</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>131889817</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>497412</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7040265</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>131889525</v>
+      </c>
+      <c r="B105" t="n">
+        <v>83244</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>497570</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7040437</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>131889777</v>
+      </c>
+      <c r="B106" t="n">
+        <v>83244</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>497473</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7040320</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>131889827</v>
+      </c>
+      <c r="B107" t="n">
+        <v>92131</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>658</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>497818</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7040505</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>131889527</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>497740</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7040504</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>131889864</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>497695</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7040309</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav här!!</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>131889828</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92215</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>497800</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7040458</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>131889797</v>
+      </c>
+      <c r="B111" t="n">
+        <v>92555</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>497512</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7040344</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>131889859</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>497784</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7040497</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt!! Flera särskilt långväxta bålar där en är över 70 cm lång.</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>131889784</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>497693</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7040594</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>131889778</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>497523</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7040132</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>131889813</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>497538</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7040327</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>131889814</v>
+      </c>
+      <c r="B116" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>497490</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7040364</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>131889839</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91846</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>497618</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7040361</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>131889850</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>497478</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7040303</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>131889836</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>497587</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7040172</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>131889882</v>
+      </c>
+      <c r="B120" t="n">
+        <v>83236</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>308</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>497616</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7040367</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>131889821</v>
+      </c>
+      <c r="B121" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>497547</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7040424</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>131889812</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>497606</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7040301</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>131889856</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>497459</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7040199</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131888330</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>131888333</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>131888307</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>131889552</v>
       </c>
       <c r="B5" t="n">
-        <v>92206</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>131888329</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888327</v>
+        <v>131888332</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,8 +1396,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1406,10 +1414,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497615</v>
+        <v>497456</v>
       </c>
       <c r="R7" t="n">
-        <v>7040418</v>
+        <v>7040270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1446,7 +1454,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,10 +1502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888332</v>
+        <v>131888324</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,16 +1530,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497456</v>
+        <v>497637</v>
       </c>
       <c r="R8" t="n">
-        <v>7040270</v>
+        <v>7040612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888324</v>
+        <v>131889559</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>91858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,26 +1639,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497637</v>
+        <v>497679</v>
       </c>
       <c r="R9" t="n">
-        <v>7040612</v>
+        <v>7040380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,11 +1702,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1754,10 +1749,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888298</v>
+        <v>131888327</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,30 +1760,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1796,10 +1787,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497697</v>
+        <v>497615</v>
       </c>
       <c r="R10" t="n">
-        <v>7040367</v>
+        <v>7040418</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1836,7 +1827,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1864,14 +1855,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1889,10 +1875,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131888302</v>
+        <v>131888298</v>
       </c>
       <c r="B11" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1931,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497492</v>
+        <v>497697</v>
       </c>
       <c r="R11" t="n">
-        <v>7040191</v>
+        <v>7040367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1969,6 +1955,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1996,12 +1987,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2019,38 +2010,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888284</v>
+        <v>131888302</v>
       </c>
       <c r="B12" t="n">
-        <v>97903</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2058,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497516</v>
+        <v>497492</v>
       </c>
       <c r="R12" t="n">
-        <v>7040157</v>
+        <v>7040191</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2109,6 +2103,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2126,37 +2140,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131889559</v>
+        <v>131888284</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>97909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2164,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497679</v>
+        <v>497516</v>
       </c>
       <c r="R13" t="n">
-        <v>7040380</v>
+        <v>7040157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2215,21 +2230,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2247,48 +2247,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131888334</v>
+        <v>131888303</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497584</v>
+        <v>497808</v>
       </c>
       <c r="R14" t="n">
-        <v>7040177</v>
+        <v>7040518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2323,18 +2340,12 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2343,19 +2354,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Naturskog dominerad av gran.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2373,65 +2374,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131888303</v>
+        <v>131888305</v>
       </c>
       <c r="B15" t="n">
-        <v>57894</v>
+        <v>91858</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100110</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus canus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497808</v>
+        <v>497587</v>
       </c>
       <c r="R15" t="n">
-        <v>7040518</v>
+        <v>7040459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2466,12 +2450,18 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar i en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2482,7 +2472,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Naturskog dominerad av gran.</t>
+          <t>Naturskog.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2500,10 +2510,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131888305</v>
+        <v>131888334</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2511,26 +2521,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2538,10 +2548,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497587</v>
+        <v>497584</v>
       </c>
       <c r="R16" t="n">
-        <v>7040459</v>
+        <v>7040177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2578,7 +2588,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Många fruktkroppar i en granhögstubbe.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2596,11 +2606,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2611,14 +2616,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
         <v>131888322</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>131888325</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131888320</v>
+        <v>131889571</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>83112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497822</v>
+        <v>497567</v>
       </c>
       <c r="R19" t="n">
-        <v>7040565</v>
+        <v>7040434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,11 +2969,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på både döda och levande granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2989,6 +2984,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2999,14 +2999,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3024,10 +3019,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131889571</v>
+        <v>131888320</v>
       </c>
       <c r="B20" t="n">
-        <v>83110</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3035,21 +3030,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497567</v>
+        <v>497822</v>
       </c>
       <c r="R20" t="n">
-        <v>7040434</v>
+        <v>7040565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3100,6 +3095,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på både döda och levande granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3115,11 +3115,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3130,9 +3125,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         <v>131888274</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>131889551</v>
       </c>
       <c r="B22" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>131889572</v>
       </c>
       <c r="B23" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131889560</v>
+        <v>131888276</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3552,24 +3552,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497653</v>
+        <v>497590</v>
       </c>
       <c r="R24" t="n">
-        <v>7040280</v>
+        <v>7040459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3617,13 +3622,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3642,9 +3651,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3662,10 +3676,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131888276</v>
+        <v>131889560</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3673,29 +3687,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3705,10 +3714,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497590</v>
+        <v>497653</v>
       </c>
       <c r="R25" t="n">
-        <v>7040459</v>
+        <v>7040280</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3743,17 +3752,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3772,14 +3777,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888277</v>
+        <v>131888299</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>91834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3808,29 +3808,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3840,10 +3839,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497615</v>
+        <v>497547</v>
       </c>
       <c r="R26" t="n">
-        <v>7040285</v>
+        <v>7040310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3880,7 +3879,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3889,6 +3888,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3907,9 +3907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3927,41 +3932,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888260</v>
+        <v>131888328</v>
       </c>
       <c r="B27" t="n">
-        <v>92555</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3969,10 +3970,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497804</v>
+        <v>497707</v>
       </c>
       <c r="R27" t="n">
-        <v>7040465</v>
+        <v>7040362</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4009,7 +4010,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fruktkroppar i en stående död gran.</t>
+          <t>Riktigt på flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4037,14 +4038,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4062,32 +4058,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888299</v>
+        <v>131888260</v>
       </c>
       <c r="B28" t="n">
-        <v>91828</v>
+        <v>92561</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4104,10 +4100,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497547</v>
+        <v>497804</v>
       </c>
       <c r="R28" t="n">
-        <v>7040310</v>
+        <v>7040465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4144,7 +4140,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4197,10 +4193,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131888328</v>
+        <v>131889566</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4235,10 +4231,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497707</v>
+        <v>497620</v>
       </c>
       <c r="R29" t="n">
-        <v>7040362</v>
+        <v>7040526</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4275,7 +4271,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Riktigt på flera granar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4291,6 +4287,11 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4323,10 +4324,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888280</v>
+        <v>131888277</v>
       </c>
       <c r="B30" t="n">
-        <v>58061</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4334,50 +4335,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497571</v>
+        <v>497615</v>
       </c>
       <c r="R30" t="n">
-        <v>7040180</v>
+        <v>7040285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4414,7 +4407,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4431,9 +4424,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4451,10 +4454,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131889566</v>
+        <v>131888280</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>58063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4462,37 +4465,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497620</v>
+        <v>497571</v>
       </c>
       <c r="R31" t="n">
-        <v>7040526</v>
+        <v>7040180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4529,7 +4545,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4538,7 +4554,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4550,21 +4565,6 @@
       <c r="AI31" t="inlineStr">
         <is>
           <t>Naturskog.</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>131889550</v>
       </c>
       <c r="B32" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>131888319</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888326</v>
+        <v>131889563</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497550</v>
+        <v>497828</v>
       </c>
       <c r="R34" t="n">
-        <v>7040497</v>
+        <v>7040520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växer här på grenar av gamla grova granar med socklar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4957,14 +4957,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4982,10 +4977,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888273</v>
+        <v>131888326</v>
       </c>
       <c r="B35" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4993,31 +4988,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5025,10 +5015,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497827</v>
+        <v>497550</v>
       </c>
       <c r="R35" t="n">
-        <v>7040466</v>
+        <v>7040497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5065,7 +5055,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran vid hyggeskanten.</t>
+          <t>Växer här på grenar av gamla grova granar med socklar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5074,6 +5064,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5094,12 +5085,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5117,10 +5108,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131889563</v>
+        <v>131889561</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>91858</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5128,26 +5119,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5155,10 +5146,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497828</v>
+        <v>497600</v>
       </c>
       <c r="R36" t="n">
-        <v>7040520</v>
+        <v>7040262</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5191,11 +5182,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5243,10 +5229,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131889561</v>
+        <v>131888273</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5254,24 +5240,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5281,10 +5272,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497600</v>
+        <v>497827</v>
       </c>
       <c r="R37" t="n">
-        <v>7040262</v>
+        <v>7040466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5319,13 +5310,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5344,9 +5339,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5367,7 +5367,7 @@
         <v>131888331</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>131888282</v>
       </c>
       <c r="B39" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>131888300</v>
       </c>
       <c r="B40" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131888301</v>
+        <v>131889567</v>
       </c>
       <c r="B41" t="n">
-        <v>91828</v>
+        <v>79266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5771,30 +5771,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5802,10 +5798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497499</v>
+        <v>497498</v>
       </c>
       <c r="R41" t="n">
-        <v>7040192</v>
+        <v>7040214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5842,7 +5838,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>I en stående döende gran.</t>
+          <t>Rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5860,6 +5856,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ41" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5870,9 +5871,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5890,10 +5896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888297</v>
+        <v>131888321</v>
       </c>
       <c r="B42" t="n">
-        <v>91828</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5901,28 +5907,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5932,10 +5938,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497565</v>
+        <v>497767</v>
       </c>
       <c r="R42" t="n">
-        <v>7040502</v>
+        <v>7040576</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5972,7 +5978,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>I stambasen av en stående döende gran.</t>
+          <t>Rikligt med garnlav på flera granar. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6000,9 +6006,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6020,10 +6031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888321</v>
+        <v>131888304</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>91858</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6031,28 +6042,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6062,10 +6069,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497767</v>
+        <v>497752</v>
       </c>
       <c r="R43" t="n">
-        <v>7040576</v>
+        <v>7040566</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6100,11 +6107,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på flera granar. Här finns fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6132,12 +6134,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6155,10 +6157,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888304</v>
+        <v>131888275</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6166,24 +6168,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6193,10 +6200,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497752</v>
+        <v>497763</v>
       </c>
       <c r="R44" t="n">
-        <v>7040566</v>
+        <v>7040580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6231,13 +6238,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6281,10 +6292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131888275</v>
+        <v>131888297</v>
       </c>
       <c r="B45" t="n">
-        <v>57902</v>
+        <v>91834</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6292,29 +6303,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6324,10 +6334,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497763</v>
+        <v>497565</v>
       </c>
       <c r="R45" t="n">
-        <v>7040580</v>
+        <v>7040502</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6364,7 +6374,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>I stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6373,6 +6383,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6391,14 +6402,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6416,10 +6422,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131889567</v>
+        <v>131889549</v>
       </c>
       <c r="B46" t="n">
-        <v>79264</v>
+        <v>91834</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6427,26 +6433,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6454,10 +6464,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497498</v>
+        <v>497841</v>
       </c>
       <c r="R46" t="n">
-        <v>7040214</v>
+        <v>7040484</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6492,11 +6502,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på flera granar.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6512,11 +6517,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ46" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6527,14 +6527,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6552,10 +6547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131889549</v>
+        <v>131888301</v>
       </c>
       <c r="B47" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6594,10 +6589,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497841</v>
+        <v>497499</v>
       </c>
       <c r="R47" t="n">
-        <v>7040484</v>
+        <v>7040192</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6630,6 +6625,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I en stående döende gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6680,7 +6680,7 @@
         <v>131888278</v>
       </c>
       <c r="B48" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>131888323</v>
       </c>
       <c r="B49" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>131888259</v>
       </c>
       <c r="B50" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>131889565</v>
       </c>
       <c r="B51" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>131888306</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889849</v>
+        <v>131889851</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497679</v>
+        <v>497564</v>
       </c>
       <c r="R53" t="n">
-        <v>7040341</v>
+        <v>7040145</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7434,11 +7434,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7471,10 +7466,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889848</v>
+        <v>131889865</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>79266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7482,26 +7477,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7509,10 +7504,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497679</v>
+        <v>497474</v>
       </c>
       <c r="R54" t="n">
-        <v>7040355</v>
+        <v>7040328</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7545,6 +7540,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mycket rikligt med garnlav här!!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7597,10 +7597,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131889851</v>
+        <v>131889848</v>
       </c>
       <c r="B55" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497564</v>
+        <v>497679</v>
       </c>
       <c r="R55" t="n">
-        <v>7040145</v>
+        <v>7040355</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7686,6 +7686,11 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7718,10 +7723,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131889865</v>
+        <v>131889775</v>
       </c>
       <c r="B56" t="n">
-        <v>79264</v>
+        <v>83246</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7729,21 +7734,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7756,10 +7761,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497474</v>
+        <v>497671</v>
       </c>
       <c r="R56" t="n">
-        <v>7040328</v>
+        <v>7040587</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7792,11 +7797,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mycket rikligt med garnlav här!!</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7849,10 +7849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889775</v>
+        <v>131889849</v>
       </c>
       <c r="B57" t="n">
-        <v>83244</v>
+        <v>91858</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7860,26 +7860,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497671</v>
+        <v>497679</v>
       </c>
       <c r="R57" t="n">
-        <v>7040587</v>
+        <v>7040341</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
         <v>131889883</v>
       </c>
       <c r="B58" t="n">
-        <v>83236</v>
+        <v>83238</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8086,37 +8086,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889526</v>
+        <v>131889796</v>
       </c>
       <c r="B59" t="n">
-        <v>83244</v>
+        <v>92561</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8124,10 +8128,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497605</v>
+        <v>497619</v>
       </c>
       <c r="R59" t="n">
-        <v>7040259</v>
+        <v>7040378</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8215,7 +8219,7 @@
         <v>131889543</v>
       </c>
       <c r="B60" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8338,10 +8342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889808</v>
+        <v>131889526</v>
       </c>
       <c r="B61" t="n">
-        <v>57902</v>
+        <v>83246</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8349,31 +8353,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8381,10 +8380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497512</v>
+        <v>497605</v>
       </c>
       <c r="R61" t="n">
-        <v>7040418</v>
+        <v>7040259</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8419,17 +8418,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8453,14 +8448,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8478,39 +8468,40 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889796</v>
+        <v>131889808</v>
       </c>
       <c r="B62" t="n">
-        <v>92555</v>
+        <v>57904</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8520,10 +8511,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497619</v>
+        <v>497512</v>
       </c>
       <c r="R62" t="n">
-        <v>7040378</v>
+        <v>7040418</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8558,13 +8549,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8588,9 +8583,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131889807</v>
+        <v>131889776</v>
       </c>
       <c r="B63" t="n">
-        <v>57902</v>
+        <v>83246</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8619,31 +8619,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8651,10 +8646,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497520</v>
+        <v>497530</v>
       </c>
       <c r="R63" t="n">
-        <v>7040421</v>
+        <v>7040312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8689,17 +8684,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8743,10 +8734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889776</v>
+        <v>131889807</v>
       </c>
       <c r="B64" t="n">
-        <v>83244</v>
+        <v>57904</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8754,26 +8745,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8781,10 +8777,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497530</v>
+        <v>497520</v>
       </c>
       <c r="R64" t="n">
-        <v>7040312</v>
+        <v>7040421</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8819,13 +8815,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>131889829</v>
       </c>
       <c r="B65" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>131889816</v>
       </c>
       <c r="B66" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>131889855</v>
       </c>
       <c r="B67" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9246,10 +9246,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889878</v>
+        <v>131889809</v>
       </c>
       <c r="B68" t="n">
-        <v>83110</v>
+        <v>57904</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9257,26 +9257,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497559</v>
+        <v>497622</v>
       </c>
       <c r="R68" t="n">
-        <v>7040336</v>
+        <v>7040347</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9322,13 +9327,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9372,10 +9381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889809</v>
+        <v>131889804</v>
       </c>
       <c r="B69" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9405,7 +9414,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9415,10 +9424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497622</v>
+        <v>497834</v>
       </c>
       <c r="R69" t="n">
-        <v>7040347</v>
+        <v>7040513</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9455,7 +9464,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9507,10 +9516,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889804</v>
+        <v>131889878</v>
       </c>
       <c r="B70" t="n">
-        <v>57902</v>
+        <v>83112</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9518,31 +9527,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9550,10 +9554,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497834</v>
+        <v>497559</v>
       </c>
       <c r="R70" t="n">
-        <v>7040513</v>
+        <v>7040336</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9588,17 +9592,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9642,10 +9642,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889531</v>
+        <v>131889834</v>
       </c>
       <c r="B71" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9653,21 +9653,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9684,10 +9684,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497831</v>
+        <v>497411</v>
       </c>
       <c r="R71" t="n">
-        <v>7040503</v>
+        <v>7040245</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9752,14 +9752,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9777,10 +9772,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889834</v>
+        <v>131889531</v>
       </c>
       <c r="B72" t="n">
-        <v>91828</v>
+        <v>91838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9788,21 +9783,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9819,10 +9814,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497411</v>
+        <v>497831</v>
       </c>
       <c r="R72" t="n">
-        <v>7040245</v>
+        <v>7040503</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9887,9 +9882,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9907,32 +9907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889528</v>
+        <v>131889783</v>
       </c>
       <c r="B73" t="n">
-        <v>91795</v>
+        <v>91838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497610</v>
+        <v>497799</v>
       </c>
       <c r="R73" t="n">
-        <v>7040287</v>
+        <v>7040466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10042,10 +10042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889534</v>
+        <v>131889785</v>
       </c>
       <c r="B74" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497640</v>
+        <v>497617</v>
       </c>
       <c r="R74" t="n">
-        <v>7040232</v>
+        <v>7040562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10137,19 +10137,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10167,10 +10172,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131889810</v>
+        <v>131889534</v>
       </c>
       <c r="B75" t="n">
-        <v>57902</v>
+        <v>91838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10178,29 +10183,28 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -10210,10 +10214,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497721</v>
+        <v>497640</v>
       </c>
       <c r="R75" t="n">
-        <v>7040314</v>
+        <v>7040232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10248,17 +10252,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -10267,11 +10267,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ75" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10282,14 +10277,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10307,32 +10297,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131889785</v>
+        <v>131889528</v>
       </c>
       <c r="B76" t="n">
-        <v>91832</v>
+        <v>91801</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10349,10 +10339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497617</v>
+        <v>497610</v>
       </c>
       <c r="R76" t="n">
-        <v>7040562</v>
+        <v>7040287</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10404,22 +10394,27 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10437,10 +10432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889783</v>
+        <v>131889810</v>
       </c>
       <c r="B77" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10448,28 +10443,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10479,10 +10475,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497799</v>
+        <v>497721</v>
       </c>
       <c r="R77" t="n">
-        <v>7040466</v>
+        <v>7040314</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10517,13 +10513,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10572,10 +10572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889863</v>
+        <v>131889869</v>
       </c>
       <c r="B78" t="n">
-        <v>79264</v>
+        <v>83112</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497565</v>
+        <v>497732</v>
       </c>
       <c r="R78" t="n">
-        <v>7040468</v>
+        <v>7040316</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10646,11 +10646,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10703,10 +10698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889869</v>
+        <v>131889863</v>
       </c>
       <c r="B79" t="n">
-        <v>83110</v>
+        <v>79266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10714,21 +10709,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10741,10 +10736,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497732</v>
+        <v>497565</v>
       </c>
       <c r="R79" t="n">
-        <v>7040316</v>
+        <v>7040468</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10777,6 +10772,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10829,10 +10829,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131889847</v>
+        <v>131889831</v>
       </c>
       <c r="B80" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10840,19 +10840,23 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
@@ -10867,10 +10871,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497569</v>
+        <v>497699</v>
       </c>
       <c r="R80" t="n">
-        <v>7040368</v>
+        <v>7040333</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10958,7 +10962,7 @@
         <v>131889838</v>
       </c>
       <c r="B81" t="n">
-        <v>91846</v>
+        <v>91852</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11085,10 +11089,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131889831</v>
+        <v>131889847</v>
       </c>
       <c r="B82" t="n">
-        <v>91828</v>
+        <v>91858</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11096,23 +11100,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497699</v>
+        <v>497569</v>
       </c>
       <c r="R82" t="n">
-        <v>7040333</v>
+        <v>7040368</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11218,7 +11218,7 @@
         <v>131889789</v>
       </c>
       <c r="B83" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>131889866</v>
       </c>
       <c r="B84" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11479,10 +11479,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889532</v>
+        <v>131889811</v>
       </c>
       <c r="B85" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11490,28 +11490,29 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11521,10 +11522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497828</v>
+        <v>497625</v>
       </c>
       <c r="R85" t="n">
-        <v>7040485</v>
+        <v>7040291</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11559,13 +11560,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11574,6 +11579,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ85" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11584,14 +11594,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11609,10 +11614,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889540</v>
+        <v>131889815</v>
       </c>
       <c r="B86" t="n">
-        <v>92131</v>
+        <v>57904</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11620,28 +11625,29 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -11651,10 +11657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497796</v>
+        <v>497472</v>
       </c>
       <c r="R86" t="n">
-        <v>7040452</v>
+        <v>7040345</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11689,13 +11695,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11719,14 +11729,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11747,7 +11752,7 @@
         <v>131889818</v>
       </c>
       <c r="B87" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11879,10 +11884,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889811</v>
+        <v>131889532</v>
       </c>
       <c r="B88" t="n">
-        <v>57902</v>
+        <v>91838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11890,29 +11895,28 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -11922,10 +11926,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497625</v>
+        <v>497828</v>
       </c>
       <c r="R88" t="n">
-        <v>7040291</v>
+        <v>7040485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11960,17 +11964,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11979,11 +11979,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ88" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11994,9 +11989,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12014,10 +12014,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889815</v>
+        <v>131889868</v>
       </c>
       <c r="B89" t="n">
-        <v>57902</v>
+        <v>83112</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12025,31 +12025,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12057,10 +12052,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497472</v>
+        <v>497696</v>
       </c>
       <c r="R89" t="n">
-        <v>7040345</v>
+        <v>7040335</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12095,17 +12090,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -12149,32 +12140,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131889795</v>
+        <v>131889540</v>
       </c>
       <c r="B90" t="n">
-        <v>92555</v>
+        <v>92137</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -12191,10 +12182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497767</v>
+        <v>497796</v>
       </c>
       <c r="R90" t="n">
-        <v>7040478</v>
+        <v>7040452</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12259,9 +12250,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12282,7 +12278,7 @@
         <v>131889880</v>
       </c>
       <c r="B91" t="n">
-        <v>89217</v>
+        <v>89223</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12414,37 +12410,41 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131889868</v>
+        <v>131889795</v>
       </c>
       <c r="B92" t="n">
-        <v>83110</v>
+        <v>92561</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12452,10 +12452,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497696</v>
+        <v>497767</v>
       </c>
       <c r="R92" t="n">
-        <v>7040335</v>
+        <v>7040478</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12540,10 +12540,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131889533</v>
+        <v>131889835</v>
       </c>
       <c r="B93" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12551,21 +12551,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -12582,10 +12582,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497784</v>
+        <v>497549</v>
       </c>
       <c r="R93" t="n">
-        <v>7040452</v>
+        <v>7040130</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12635,6 +12635,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ93" t="inlineStr">
         <is>
           <t>gran</t>
@@ -12645,14 +12650,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12670,61 +12670,52 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131889823</v>
+        <v>131889533</v>
       </c>
       <c r="B94" t="n">
-        <v>57743</v>
+        <v>91838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497598</v>
+        <v>497784</v>
       </c>
       <c r="R94" t="n">
-        <v>7040321</v>
+        <v>7040452</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12765,6 +12756,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -12773,9 +12765,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12793,52 +12800,61 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131889835</v>
+        <v>131889823</v>
       </c>
       <c r="B95" t="n">
-        <v>91828</v>
+        <v>57745</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1108</v>
+        <v>102621</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497549</v>
+        <v>497598</v>
       </c>
       <c r="R95" t="n">
-        <v>7040130</v>
+        <v>7040321</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12879,7 +12895,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12891,21 +12906,6 @@
       <c r="AI95" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131889853</v>
+        <v>131889786</v>
       </c>
       <c r="B96" t="n">
-        <v>91852</v>
+        <v>91838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12934,19 +12934,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
@@ -12961,10 +12965,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497592</v>
+        <v>497661</v>
       </c>
       <c r="R96" t="n">
-        <v>7040180</v>
+        <v>7040289</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13049,10 +13053,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131889786</v>
+        <v>131889853</v>
       </c>
       <c r="B97" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13060,23 +13064,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -13091,10 +13091,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497661</v>
+        <v>497592</v>
       </c>
       <c r="R97" t="n">
-        <v>7040289</v>
+        <v>7040180</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13179,10 +13179,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131889805</v>
+        <v>131889852</v>
       </c>
       <c r="B98" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13190,29 +13190,24 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -13222,10 +13217,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497802</v>
+        <v>497574</v>
       </c>
       <c r="R98" t="n">
-        <v>7040466</v>
+        <v>7040148</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13260,17 +13255,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13314,10 +13305,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889806</v>
+        <v>131889881</v>
       </c>
       <c r="B99" t="n">
-        <v>57902</v>
+        <v>83238</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13325,31 +13316,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13357,10 +13343,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497569</v>
+        <v>497527</v>
       </c>
       <c r="R99" t="n">
-        <v>7040455</v>
+        <v>7040360</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13395,17 +13381,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13417,21 +13399,6 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13449,10 +13416,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131889819</v>
+        <v>131889805</v>
       </c>
       <c r="B100" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13492,10 +13459,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497516</v>
+        <v>497802</v>
       </c>
       <c r="R100" t="n">
-        <v>7040136</v>
+        <v>7040466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13584,10 +13551,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131889852</v>
+        <v>131889806</v>
       </c>
       <c r="B101" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13595,24 +13562,29 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -13622,10 +13594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497574</v>
+        <v>497569</v>
       </c>
       <c r="R101" t="n">
-        <v>7040148</v>
+        <v>7040455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13660,13 +13632,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13710,10 +13686,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131889881</v>
+        <v>131889819</v>
       </c>
       <c r="B102" t="n">
-        <v>83236</v>
+        <v>57904</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13721,26 +13697,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13748,10 +13729,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497527</v>
+        <v>497516</v>
       </c>
       <c r="R102" t="n">
-        <v>7040360</v>
+        <v>7040136</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13786,13 +13767,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13804,6 +13789,21 @@
       <c r="AI102" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
         <v>131889542</v>
       </c>
       <c r="B103" t="n">
-        <v>78276</v>
+        <v>78278</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>131889817</v>
       </c>
       <c r="B104" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889525</v>
+        <v>131889827</v>
       </c>
       <c r="B105" t="n">
-        <v>83244</v>
+        <v>92137</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,26 +14088,30 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14115,10 +14119,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497570</v>
+        <v>497818</v>
       </c>
       <c r="R105" t="n">
-        <v>7040437</v>
+        <v>7040505</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14168,11 +14172,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14183,9 +14182,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14206,7 +14210,7 @@
         <v>131889777</v>
       </c>
       <c r="B106" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14329,10 +14333,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131889827</v>
+        <v>131889525</v>
       </c>
       <c r="B107" t="n">
-        <v>92131</v>
+        <v>83246</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14340,30 +14344,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14371,10 +14371,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497818</v>
+        <v>497570</v>
       </c>
       <c r="R107" t="n">
-        <v>7040505</v>
+        <v>7040437</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14424,6 +14424,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ107" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14434,14 +14439,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14462,7 +14462,7 @@
         <v>131889527</v>
       </c>
       <c r="B108" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>131889864</v>
       </c>
       <c r="B109" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14723,32 +14723,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131889828</v>
+        <v>131889797</v>
       </c>
       <c r="B110" t="n">
-        <v>92215</v>
+        <v>92561</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497800</v>
+        <v>497512</v>
       </c>
       <c r="R110" t="n">
-        <v>7040458</v>
+        <v>7040344</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14816,11 +14816,6 @@
       <c r="AH110" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -14853,10 +14848,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131889797</v>
+        <v>131889778</v>
       </c>
       <c r="B111" t="n">
-        <v>92555</v>
+        <v>91801</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14864,30 +14859,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -14895,10 +14886,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497512</v>
+        <v>497523</v>
       </c>
       <c r="R111" t="n">
-        <v>7040344</v>
+        <v>7040132</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14946,6 +14937,11 @@
       <c r="AH111" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -14981,7 +14977,7 @@
         <v>131889859</v>
       </c>
       <c r="B112" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15112,10 +15108,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131889784</v>
+        <v>131889813</v>
       </c>
       <c r="B113" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15123,28 +15119,29 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -15154,10 +15151,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497693</v>
+        <v>497538</v>
       </c>
       <c r="R113" t="n">
-        <v>7040594</v>
+        <v>7040327</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15192,13 +15189,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -15242,37 +15243,41 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131889778</v>
+        <v>131889784</v>
       </c>
       <c r="B114" t="n">
-        <v>91795</v>
+        <v>91838</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15280,10 +15285,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497523</v>
+        <v>497693</v>
       </c>
       <c r="R114" t="n">
-        <v>7040132</v>
+        <v>7040594</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15368,40 +15373,39 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131889813</v>
+        <v>131889828</v>
       </c>
       <c r="B115" t="n">
-        <v>57902</v>
+        <v>92221</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -15411,10 +15415,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497538</v>
+        <v>497800</v>
       </c>
       <c r="R115" t="n">
-        <v>7040327</v>
+        <v>7040458</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15449,17 +15453,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -15503,10 +15503,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131889814</v>
+        <v>131889839</v>
       </c>
       <c r="B116" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15514,29 +15514,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -15546,10 +15545,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497490</v>
+        <v>497618</v>
       </c>
       <c r="R116" t="n">
-        <v>7040364</v>
+        <v>7040361</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15584,17 +15583,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -15638,10 +15633,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131889839</v>
+        <v>131889814</v>
       </c>
       <c r="B117" t="n">
-        <v>91846</v>
+        <v>57904</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15649,28 +15644,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15680,10 +15676,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497618</v>
+        <v>497490</v>
       </c>
       <c r="R117" t="n">
-        <v>7040361</v>
+        <v>7040364</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15718,13 +15714,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15768,10 +15768,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131889850</v>
+        <v>131889882</v>
       </c>
       <c r="B118" t="n">
-        <v>91852</v>
+        <v>83238</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15779,26 +15779,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15806,10 +15806,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497478</v>
+        <v>497616</v>
       </c>
       <c r="R118" t="n">
-        <v>7040303</v>
+        <v>7040367</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15862,21 +15862,6 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15897,7 +15882,7 @@
         <v>131889836</v>
       </c>
       <c r="B119" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16024,10 +16009,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131889882</v>
+        <v>131889850</v>
       </c>
       <c r="B120" t="n">
-        <v>83236</v>
+        <v>91858</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16035,26 +16020,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -16062,10 +16047,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>497616</v>
+        <v>497478</v>
       </c>
       <c r="R120" t="n">
-        <v>7040367</v>
+        <v>7040303</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16118,6 +16103,21 @@
       <c r="AI120" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131889821</v>
+        <v>131889856</v>
       </c>
       <c r="B121" t="n">
-        <v>58061</v>
+        <v>91858</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16146,50 +16146,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>497547</v>
+        <v>497459</v>
       </c>
       <c r="R121" t="n">
-        <v>7040424</v>
+        <v>7040199</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16230,6 +16217,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -16238,9 +16226,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16258,10 +16256,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131889812</v>
+        <v>131889821</v>
       </c>
       <c r="B122" t="n">
-        <v>57902</v>
+        <v>58063</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16269,42 +16267,50 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>497606</v>
+        <v>497547</v>
       </c>
       <c r="R122" t="n">
-        <v>7040301</v>
+        <v>7040424</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16339,11 +16345,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -16361,21 +16362,6 @@
       <c r="AI122" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16393,10 +16379,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131889856</v>
+        <v>131889812</v>
       </c>
       <c r="B123" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16404,24 +16390,29 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -16431,10 +16422,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>497459</v>
+        <v>497606</v>
       </c>
       <c r="R123" t="n">
-        <v>7040199</v>
+        <v>7040301</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16469,13 +16460,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -16484,19 +16479,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -675,45 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131888330</v>
+        <v>131889552</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>92212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497598</v>
+        <v>497603</v>
       </c>
       <c r="R2" t="n">
-        <v>7040306</v>
+        <v>7040263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på många granar.</t>
+          <t>Växer på gammal fruktkropp av granticka på en stubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,24 +775,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Naturskog med rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +815,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131888333</v>
+        <v>131888330</v>
       </c>
       <c r="B3" t="n">
         <v>79266</v>
@@ -844,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497455</v>
+        <v>497598</v>
       </c>
       <c r="R3" t="n">
-        <v>7040215</v>
+        <v>7040306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket rikligt med garnlav på många granar.</t>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -953,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131888307</v>
+        <v>131888333</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,26 +965,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -991,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497644</v>
+        <v>497455</v>
       </c>
       <c r="R4" t="n">
-        <v>7040292</v>
+        <v>7040215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en grov knäckt död gran med 42 cm i brösthöjdsdiameter.</t>
+          <t>Mycket rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,11 +1058,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1066,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,34 +1093,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131889552</v>
+        <v>131888307</v>
       </c>
       <c r="B5" t="n">
-        <v>92212</v>
+        <v>91858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497603</v>
+        <v>497644</v>
       </c>
       <c r="R5" t="n">
-        <v>7040263</v>
+        <v>7040292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på gammal fruktkropp av granticka på en stubbe.</t>
+          <t>Gott om fruktkroppar i en grov knäckt död gran med 42 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,27 +1191,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Naturskog med rikliga mängder död ved.</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1368,45 +1368,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888332</v>
+        <v>131888284</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>97909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1414,10 +1407,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497456</v>
+        <v>497516</v>
       </c>
       <c r="R7" t="n">
-        <v>7040270</v>
+        <v>7040157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,11 +1445,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1470,21 +1458,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1502,7 +1475,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888324</v>
+        <v>131888332</v>
       </c>
       <c r="B8" t="n">
         <v>79266</v>
@@ -1530,8 +1503,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1540,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497637</v>
+        <v>497456</v>
       </c>
       <c r="R8" t="n">
-        <v>7040612</v>
+        <v>7040270</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1580,7 +1561,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131889559</v>
+        <v>131888324</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1639,26 +1620,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1666,10 +1647,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497679</v>
+        <v>497637</v>
       </c>
       <c r="R9" t="n">
-        <v>7040380</v>
+        <v>7040612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,6 +1683,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1749,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888327</v>
+        <v>131889559</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1760,26 +1746,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1787,10 +1773,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497615</v>
+        <v>497679</v>
       </c>
       <c r="R10" t="n">
-        <v>7040418</v>
+        <v>7040380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,11 +1809,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1875,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131888298</v>
+        <v>131888327</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,30 +1867,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1917,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497697</v>
+        <v>497615</v>
       </c>
       <c r="R11" t="n">
-        <v>7040367</v>
+        <v>7040418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1957,7 +1934,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1985,14 +1962,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2010,7 +1982,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888302</v>
+        <v>131888298</v>
       </c>
       <c r="B12" t="n">
         <v>91834</v>
@@ -2052,10 +2024,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497492</v>
+        <v>497697</v>
       </c>
       <c r="R12" t="n">
-        <v>7040191</v>
+        <v>7040367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2090,6 +2062,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2117,12 +2094,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2140,38 +2117,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888284</v>
+        <v>131888302</v>
       </c>
       <c r="B13" t="n">
-        <v>97909</v>
+        <v>91834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2179,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497516</v>
+        <v>497492</v>
       </c>
       <c r="R13" t="n">
-        <v>7040157</v>
+        <v>7040191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2230,6 +2210,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131888274</v>
+        <v>131889551</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3161,29 +3161,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3193,10 +3192,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497820</v>
+        <v>497544</v>
       </c>
       <c r="R21" t="n">
-        <v>7040580</v>
+        <v>7040208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3231,23 +3230,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131889551</v>
+        <v>131889572</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>83112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3291,30 +3291,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3322,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497544</v>
+        <v>497575</v>
       </c>
       <c r="R22" t="n">
-        <v>7040208</v>
+        <v>7040219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3390,9 +3386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3411,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131889572</v>
+        <v>131888274</v>
       </c>
       <c r="B23" t="n">
-        <v>83112</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3421,26 +3422,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3448,10 +3454,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497575</v>
+        <v>497820</v>
       </c>
       <c r="R23" t="n">
-        <v>7040219</v>
+        <v>7040580</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3486,13 +3492,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3501,11 +3511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3516,14 +3521,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888328</v>
+        <v>131888277</v>
       </c>
       <c r="B27" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3943,26 +3943,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3970,10 +3975,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497707</v>
+        <v>497615</v>
       </c>
       <c r="R27" t="n">
-        <v>7040362</v>
+        <v>7040285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4010,7 +4015,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Riktigt på flera granar.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4019,7 +4024,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4058,41 +4062,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888260</v>
+        <v>131888328</v>
       </c>
       <c r="B28" t="n">
-        <v>92561</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497804</v>
+        <v>497707</v>
       </c>
       <c r="R28" t="n">
-        <v>7040465</v>
+        <v>7040362</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Fruktkroppar i en stående död gran.</t>
+          <t>Riktigt på flera granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4168,14 +4168,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4193,37 +4188,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131889566</v>
+        <v>131888260</v>
       </c>
       <c r="B29" t="n">
-        <v>79266</v>
+        <v>92561</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4231,10 +4230,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497620</v>
+        <v>497804</v>
       </c>
       <c r="R29" t="n">
-        <v>7040526</v>
+        <v>7040465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4271,7 +4270,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4289,11 +4288,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ29" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4304,9 +4298,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4324,10 +4323,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888277</v>
+        <v>131889566</v>
       </c>
       <c r="B30" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4335,31 +4334,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4367,10 +4361,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497615</v>
+        <v>497620</v>
       </c>
       <c r="R30" t="n">
-        <v>7040285</v>
+        <v>7040526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4407,7 +4401,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4416,12 +4410,18 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -6677,10 +6677,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131888278</v>
+        <v>131888323</v>
       </c>
       <c r="B48" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6688,31 +6688,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6720,10 +6715,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497622</v>
+        <v>497679</v>
       </c>
       <c r="R48" t="n">
-        <v>7040297</v>
+        <v>7040625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6760,7 +6755,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6769,6 +6764,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6777,11 +6773,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6794,12 +6785,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6817,10 +6808,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131888323</v>
+        <v>131888278</v>
       </c>
       <c r="B49" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6828,26 +6819,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6855,10 +6851,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497679</v>
+        <v>497622</v>
       </c>
       <c r="R49" t="n">
-        <v>7040625</v>
+        <v>7040297</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6895,7 +6891,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6904,7 +6900,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6913,6 +6908,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
+        </is>
+      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889851</v>
+        <v>131889883</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>83238</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7356,26 +7356,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497564</v>
+        <v>497621</v>
       </c>
       <c r="R53" t="n">
-        <v>7040145</v>
+        <v>7040366</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7436,19 +7436,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7466,10 +7456,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889865</v>
+        <v>131889851</v>
       </c>
       <c r="B54" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7477,26 +7467,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7504,10 +7494,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497474</v>
+        <v>497564</v>
       </c>
       <c r="R54" t="n">
-        <v>7040328</v>
+        <v>7040145</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7542,11 +7532,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mycket rikligt med garnlav här!!</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7560,11 +7545,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7597,10 +7577,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131889848</v>
+        <v>131889865</v>
       </c>
       <c r="B55" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7608,26 +7588,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7635,10 +7615,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497679</v>
+        <v>497474</v>
       </c>
       <c r="R55" t="n">
-        <v>7040355</v>
+        <v>7040328</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7671,6 +7651,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Mycket rikligt med garnlav här!!</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7723,10 +7708,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131889775</v>
+        <v>131889848</v>
       </c>
       <c r="B56" t="n">
-        <v>83246</v>
+        <v>91858</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7734,26 +7719,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7761,10 +7746,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497671</v>
+        <v>497679</v>
       </c>
       <c r="R56" t="n">
-        <v>7040587</v>
+        <v>7040355</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7849,10 +7834,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889849</v>
+        <v>131889775</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
+        <v>83246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7860,26 +7845,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7887,10 +7872,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497679</v>
+        <v>497671</v>
       </c>
       <c r="R57" t="n">
-        <v>7040341</v>
+        <v>7040587</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7975,10 +7960,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131889883</v>
+        <v>131889849</v>
       </c>
       <c r="B58" t="n">
-        <v>83238</v>
+        <v>91858</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7986,26 +7971,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8013,10 +7998,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497621</v>
+        <v>497679</v>
       </c>
       <c r="R58" t="n">
-        <v>7040366</v>
+        <v>7040341</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8069,6 +8054,21 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8216,10 +8216,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889543</v>
+        <v>131889808</v>
       </c>
       <c r="B60" t="n">
-        <v>78278</v>
+        <v>57904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8227,26 +8227,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8254,10 +8259,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497577</v>
+        <v>497512</v>
       </c>
       <c r="R60" t="n">
-        <v>7040217</v>
+        <v>7040418</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8292,13 +8297,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8309,7 +8318,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8322,9 +8331,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8342,10 +8356,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889526</v>
+        <v>131889543</v>
       </c>
       <c r="B61" t="n">
-        <v>83246</v>
+        <v>78278</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8353,21 +8367,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8380,10 +8394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497605</v>
+        <v>497577</v>
       </c>
       <c r="R61" t="n">
-        <v>7040259</v>
+        <v>7040217</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8435,7 +8449,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8468,10 +8482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889808</v>
+        <v>131889526</v>
       </c>
       <c r="B62" t="n">
-        <v>57904</v>
+        <v>83246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8479,31 +8493,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8511,10 +8520,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497512</v>
+        <v>497605</v>
       </c>
       <c r="R62" t="n">
-        <v>7040418</v>
+        <v>7040259</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8549,17 +8558,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8583,14 +8588,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131889816</v>
+        <v>131889855</v>
       </c>
       <c r="B66" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8991,29 +8991,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9023,10 +9018,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497433</v>
+        <v>497671</v>
       </c>
       <c r="R66" t="n">
-        <v>7040274</v>
+        <v>7040299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9061,17 +9056,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -9082,7 +9073,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9095,14 +9086,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9120,10 +9106,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889855</v>
+        <v>131889816</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9131,24 +9117,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9158,10 +9149,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497671</v>
+        <v>497433</v>
       </c>
       <c r="R67" t="n">
-        <v>7040299</v>
+        <v>7040274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9196,13 +9187,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9226,9 +9221,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -11479,40 +11479,39 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889811</v>
+        <v>131889795</v>
       </c>
       <c r="B85" t="n">
-        <v>57904</v>
+        <v>92561</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11522,10 +11521,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497625</v>
+        <v>497767</v>
       </c>
       <c r="R85" t="n">
-        <v>7040291</v>
+        <v>7040478</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11560,17 +11559,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11614,10 +11609,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889815</v>
+        <v>131889532</v>
       </c>
       <c r="B86" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11625,29 +11620,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -11657,10 +11651,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497472</v>
+        <v>497828</v>
       </c>
       <c r="R86" t="n">
-        <v>7040345</v>
+        <v>7040485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11695,17 +11689,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11714,11 +11704,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ86" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11729,9 +11714,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11749,10 +11739,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889818</v>
+        <v>131889868</v>
       </c>
       <c r="B87" t="n">
-        <v>57904</v>
+        <v>83112</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11760,31 +11750,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11792,10 +11777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497444</v>
+        <v>497696</v>
       </c>
       <c r="R87" t="n">
-        <v>7040224</v>
+        <v>7040335</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11830,17 +11815,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11884,10 +11865,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889532</v>
+        <v>131889540</v>
       </c>
       <c r="B88" t="n">
-        <v>91838</v>
+        <v>92137</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11895,21 +11876,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11926,10 +11907,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497828</v>
+        <v>497796</v>
       </c>
       <c r="R88" t="n">
-        <v>7040485</v>
+        <v>7040452</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11977,6 +11958,11 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12014,10 +12000,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889868</v>
+        <v>131889880</v>
       </c>
       <c r="B89" t="n">
-        <v>83112</v>
+        <v>89223</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12025,26 +12011,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12052,10 +12042,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497696</v>
+        <v>497791</v>
       </c>
       <c r="R89" t="n">
-        <v>7040335</v>
+        <v>7040457</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12120,9 +12110,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12140,10 +12135,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131889540</v>
+        <v>131889811</v>
       </c>
       <c r="B90" t="n">
-        <v>92137</v>
+        <v>57904</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12151,28 +12146,29 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -12182,10 +12178,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497796</v>
+        <v>497625</v>
       </c>
       <c r="R90" t="n">
-        <v>7040452</v>
+        <v>7040291</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12220,13 +12216,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12250,14 +12250,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12275,10 +12270,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131889880</v>
+        <v>131889815</v>
       </c>
       <c r="B91" t="n">
-        <v>89223</v>
+        <v>57904</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12286,28 +12281,29 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12317,10 +12313,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497791</v>
+        <v>497472</v>
       </c>
       <c r="R91" t="n">
-        <v>7040457</v>
+        <v>7040345</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12355,13 +12351,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12385,14 +12385,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12410,39 +12405,40 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131889795</v>
+        <v>131889818</v>
       </c>
       <c r="B92" t="n">
-        <v>92561</v>
+        <v>57904</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -12452,10 +12448,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497767</v>
+        <v>497444</v>
       </c>
       <c r="R92" t="n">
-        <v>7040478</v>
+        <v>7040224</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12490,13 +12486,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889827</v>
+        <v>131889777</v>
       </c>
       <c r="B105" t="n">
-        <v>92137</v>
+        <v>83246</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,30 +14088,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14119,10 +14115,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497818</v>
+        <v>497473</v>
       </c>
       <c r="R105" t="n">
-        <v>7040505</v>
+        <v>7040320</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14172,6 +14168,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14182,14 +14183,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14207,10 +14203,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889777</v>
+        <v>131889827</v>
       </c>
       <c r="B106" t="n">
-        <v>83246</v>
+        <v>92137</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14218,26 +14214,30 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497473</v>
+        <v>497818</v>
       </c>
       <c r="R106" t="n">
-        <v>7040320</v>
+        <v>7040505</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14298,11 +14298,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14313,9 +14308,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -1368,38 +1368,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888284</v>
+        <v>131888298</v>
       </c>
       <c r="B7" t="n">
-        <v>97909</v>
+        <v>91834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1407,10 +1410,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497516</v>
+        <v>497697</v>
       </c>
       <c r="R7" t="n">
-        <v>7040157</v>
+        <v>7040367</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1445,6 +1448,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1458,6 +1466,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1475,10 +1503,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888332</v>
+        <v>131888302</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>91834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,34 +1514,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1521,10 +1545,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497456</v>
+        <v>497492</v>
       </c>
       <c r="R8" t="n">
-        <v>7040270</v>
+        <v>7040191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,11 +1583,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1589,9 +1608,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,7 +1633,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888324</v>
+        <v>131888332</v>
       </c>
       <c r="B9" t="n">
         <v>79266</v>
@@ -1637,8 +1661,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1647,10 +1679,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497637</v>
+        <v>497456</v>
       </c>
       <c r="R9" t="n">
-        <v>7040612</v>
+        <v>7040270</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1719,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1735,10 +1767,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131889559</v>
+        <v>131888324</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,26 +1778,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1773,10 +1805,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497679</v>
+        <v>497637</v>
       </c>
       <c r="R10" t="n">
-        <v>7040380</v>
+        <v>7040612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,6 +1841,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1856,10 +1893,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131888327</v>
+        <v>131889559</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,26 +1904,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1894,10 +1931,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497615</v>
+        <v>497679</v>
       </c>
       <c r="R11" t="n">
-        <v>7040418</v>
+        <v>7040380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,11 +1967,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,10 +2014,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888298</v>
+        <v>131888327</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,30 +2025,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2024,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497697</v>
+        <v>497615</v>
       </c>
       <c r="R12" t="n">
-        <v>7040367</v>
+        <v>7040418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2092,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2092,14 +2120,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2117,41 +2140,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888302</v>
+        <v>131888284</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>97909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2159,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497492</v>
+        <v>497516</v>
       </c>
       <c r="R13" t="n">
-        <v>7040191</v>
+        <v>7040157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2210,26 +2230,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131889776</v>
+        <v>131889829</v>
       </c>
       <c r="B63" t="n">
-        <v>83246</v>
+        <v>78278</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8619,21 +8619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497530</v>
+        <v>497561</v>
       </c>
       <c r="R63" t="n">
-        <v>7040312</v>
+        <v>7040467</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8702,21 +8702,6 @@
       <c r="AI63" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8734,10 +8719,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889807</v>
+        <v>131889776</v>
       </c>
       <c r="B64" t="n">
-        <v>57904</v>
+        <v>83246</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8745,31 +8730,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8777,10 +8757,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497520</v>
+        <v>497530</v>
       </c>
       <c r="R64" t="n">
-        <v>7040421</v>
+        <v>7040312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8815,17 +8795,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8869,10 +8845,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889829</v>
+        <v>131889807</v>
       </c>
       <c r="B65" t="n">
-        <v>78278</v>
+        <v>57904</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8880,26 +8856,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8907,10 +8888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497561</v>
+        <v>497520</v>
       </c>
       <c r="R65" t="n">
-        <v>7040467</v>
+        <v>7040421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8945,13 +8926,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8963,6 +8948,21 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131889855</v>
+        <v>131889816</v>
       </c>
       <c r="B66" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8991,24 +8991,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9018,10 +9023,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497671</v>
+        <v>497433</v>
       </c>
       <c r="R66" t="n">
-        <v>7040299</v>
+        <v>7040274</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9056,13 +9061,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -9073,7 +9082,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9086,9 +9095,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9106,10 +9120,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889816</v>
+        <v>131889855</v>
       </c>
       <c r="B67" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9117,29 +9131,24 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9149,10 +9158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497433</v>
+        <v>497671</v>
       </c>
       <c r="R67" t="n">
-        <v>7040274</v>
+        <v>7040299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9187,17 +9196,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9208,7 +9213,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9221,14 +9226,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9246,10 +9246,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889809</v>
+        <v>131889878</v>
       </c>
       <c r="B68" t="n">
-        <v>57904</v>
+        <v>83112</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9257,31 +9257,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497622</v>
+        <v>497559</v>
       </c>
       <c r="R68" t="n">
-        <v>7040347</v>
+        <v>7040336</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9327,17 +9322,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9381,10 +9372,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889804</v>
+        <v>131889834</v>
       </c>
       <c r="B69" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9392,29 +9383,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9424,10 +9414,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497834</v>
+        <v>497411</v>
       </c>
       <c r="R69" t="n">
-        <v>7040513</v>
+        <v>7040245</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9462,17 +9452,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9516,10 +9502,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889878</v>
+        <v>131889531</v>
       </c>
       <c r="B70" t="n">
-        <v>83112</v>
+        <v>91838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9527,26 +9513,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9554,10 +9544,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497559</v>
+        <v>497831</v>
       </c>
       <c r="R70" t="n">
-        <v>7040336</v>
+        <v>7040503</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9622,9 +9612,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9642,10 +9637,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889834</v>
+        <v>131889809</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9653,28 +9648,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9684,10 +9680,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497411</v>
+        <v>497622</v>
       </c>
       <c r="R71" t="n">
-        <v>7040245</v>
+        <v>7040347</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9722,13 +9718,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889531</v>
+        <v>131889804</v>
       </c>
       <c r="B72" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9783,28 +9783,29 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9814,10 +9815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497831</v>
+        <v>497834</v>
       </c>
       <c r="R72" t="n">
-        <v>7040503</v>
+        <v>7040513</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9852,13 +9853,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9882,14 +9887,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10572,10 +10572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889869</v>
+        <v>131889863</v>
       </c>
       <c r="B78" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497732</v>
+        <v>497565</v>
       </c>
       <c r="R78" t="n">
-        <v>7040316</v>
+        <v>7040468</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10646,6 +10646,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10698,10 +10703,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889863</v>
+        <v>131889869</v>
       </c>
       <c r="B79" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10709,21 +10714,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10736,10 +10741,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497565</v>
+        <v>497732</v>
       </c>
       <c r="R79" t="n">
-        <v>7040468</v>
+        <v>7040316</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10772,11 +10777,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11479,39 +11479,40 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889795</v>
+        <v>131889811</v>
       </c>
       <c r="B85" t="n">
-        <v>92561</v>
+        <v>57904</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11521,10 +11522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497767</v>
+        <v>497625</v>
       </c>
       <c r="R85" t="n">
-        <v>7040478</v>
+        <v>7040291</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11559,13 +11560,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11609,10 +11614,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889532</v>
+        <v>131889815</v>
       </c>
       <c r="B86" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11620,28 +11625,29 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -11651,10 +11657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497828</v>
+        <v>497472</v>
       </c>
       <c r="R86" t="n">
-        <v>7040485</v>
+        <v>7040345</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11689,13 +11695,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11704,6 +11714,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ86" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11714,14 +11729,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11739,10 +11749,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889868</v>
+        <v>131889818</v>
       </c>
       <c r="B87" t="n">
-        <v>83112</v>
+        <v>57904</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11750,26 +11760,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11777,10 +11792,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497696</v>
+        <v>497444</v>
       </c>
       <c r="R87" t="n">
-        <v>7040335</v>
+        <v>7040224</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11815,13 +11830,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11865,10 +11884,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889540</v>
+        <v>131889532</v>
       </c>
       <c r="B88" t="n">
-        <v>92137</v>
+        <v>91838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11876,21 +11895,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11907,10 +11926,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497796</v>
+        <v>497828</v>
       </c>
       <c r="R88" t="n">
-        <v>7040452</v>
+        <v>7040485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11958,11 +11977,6 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12000,10 +12014,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889880</v>
+        <v>131889868</v>
       </c>
       <c r="B89" t="n">
-        <v>89223</v>
+        <v>83112</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12011,30 +12025,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12042,10 +12052,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497791</v>
+        <v>497696</v>
       </c>
       <c r="R89" t="n">
-        <v>7040457</v>
+        <v>7040335</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12110,14 +12120,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12135,10 +12140,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131889811</v>
+        <v>131889540</v>
       </c>
       <c r="B90" t="n">
-        <v>57904</v>
+        <v>92137</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12146,29 +12151,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -12178,10 +12182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497625</v>
+        <v>497796</v>
       </c>
       <c r="R90" t="n">
-        <v>7040291</v>
+        <v>7040452</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12216,17 +12220,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12250,9 +12250,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12270,10 +12275,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131889815</v>
+        <v>131889880</v>
       </c>
       <c r="B91" t="n">
-        <v>57904</v>
+        <v>89223</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12281,29 +12286,28 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12313,10 +12317,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497472</v>
+        <v>497791</v>
       </c>
       <c r="R91" t="n">
-        <v>7040345</v>
+        <v>7040457</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12351,17 +12355,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12385,9 +12385,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12405,40 +12410,39 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131889818</v>
+        <v>131889795</v>
       </c>
       <c r="B92" t="n">
-        <v>57904</v>
+        <v>92561</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -12448,10 +12452,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497444</v>
+        <v>497767</v>
       </c>
       <c r="R92" t="n">
-        <v>7040224</v>
+        <v>7040478</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12486,17 +12490,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13305,10 +13305,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889881</v>
+        <v>131889805</v>
       </c>
       <c r="B99" t="n">
-        <v>83238</v>
+        <v>57904</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13316,26 +13316,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13343,10 +13348,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497527</v>
+        <v>497802</v>
       </c>
       <c r="R99" t="n">
-        <v>7040360</v>
+        <v>7040466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13381,13 +13386,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13399,6 +13408,21 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13416,7 +13440,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131889805</v>
+        <v>131889806</v>
       </c>
       <c r="B100" t="n">
         <v>57904</v>
@@ -13459,10 +13483,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497802</v>
+        <v>497569</v>
       </c>
       <c r="R100" t="n">
-        <v>7040466</v>
+        <v>7040455</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13551,7 +13575,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131889806</v>
+        <v>131889819</v>
       </c>
       <c r="B101" t="n">
         <v>57904</v>
@@ -13594,10 +13618,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497569</v>
+        <v>497516</v>
       </c>
       <c r="R101" t="n">
-        <v>7040455</v>
+        <v>7040136</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13686,10 +13710,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131889819</v>
+        <v>131889881</v>
       </c>
       <c r="B102" t="n">
-        <v>57904</v>
+        <v>83238</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13697,31 +13721,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13729,10 +13748,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497516</v>
+        <v>497527</v>
       </c>
       <c r="R102" t="n">
-        <v>7040136</v>
+        <v>7040360</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13767,17 +13786,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13789,21 +13804,6 @@
       <c r="AI102" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131889856</v>
+        <v>131889812</v>
       </c>
       <c r="B121" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16146,24 +16146,29 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -16173,10 +16178,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>497459</v>
+        <v>497606</v>
       </c>
       <c r="R121" t="n">
-        <v>7040199</v>
+        <v>7040301</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16211,13 +16216,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -16226,19 +16235,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16379,10 +16393,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131889812</v>
+        <v>131889856</v>
       </c>
       <c r="B123" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16390,29 +16404,24 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
@@ -16422,10 +16431,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>497606</v>
+        <v>497459</v>
       </c>
       <c r="R123" t="n">
-        <v>7040301</v>
+        <v>7040199</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16460,17 +16469,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -16479,24 +16484,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -3541,10 +3541,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888276</v>
+        <v>131889560</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3552,29 +3552,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497590</v>
+        <v>497653</v>
       </c>
       <c r="R24" t="n">
-        <v>7040459</v>
+        <v>7040280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,17 +3617,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3651,14 +3642,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3676,10 +3662,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131889560</v>
+        <v>131888276</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3687,24 +3673,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3714,10 +3705,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497653</v>
+        <v>497590</v>
       </c>
       <c r="R25" t="n">
-        <v>7040280</v>
+        <v>7040459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3752,13 +3743,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,9 +3772,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -9246,10 +9246,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889878</v>
+        <v>131889809</v>
       </c>
       <c r="B68" t="n">
-        <v>83112</v>
+        <v>57904</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9257,26 +9257,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497559</v>
+        <v>497622</v>
       </c>
       <c r="R68" t="n">
-        <v>7040336</v>
+        <v>7040347</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9322,13 +9327,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9372,10 +9381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889834</v>
+        <v>131889804</v>
       </c>
       <c r="B69" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9383,28 +9392,29 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9414,10 +9424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497411</v>
+        <v>497834</v>
       </c>
       <c r="R69" t="n">
-        <v>7040245</v>
+        <v>7040513</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9452,13 +9462,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9502,10 +9516,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889531</v>
+        <v>131889878</v>
       </c>
       <c r="B70" t="n">
-        <v>91838</v>
+        <v>83112</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9513,30 +9527,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9544,10 +9554,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497831</v>
+        <v>497559</v>
       </c>
       <c r="R70" t="n">
-        <v>7040503</v>
+        <v>7040336</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9612,14 +9622,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9637,10 +9642,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889809</v>
+        <v>131889834</v>
       </c>
       <c r="B71" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9648,29 +9653,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9680,10 +9684,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497622</v>
+        <v>497411</v>
       </c>
       <c r="R71" t="n">
-        <v>7040347</v>
+        <v>7040245</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9718,17 +9722,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889804</v>
+        <v>131889531</v>
       </c>
       <c r="B72" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9783,29 +9783,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9815,10 +9814,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497834</v>
+        <v>497831</v>
       </c>
       <c r="R72" t="n">
-        <v>7040513</v>
+        <v>7040503</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9853,17 +9852,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9887,9 +9882,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -11479,40 +11479,39 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889811</v>
+        <v>131889795</v>
       </c>
       <c r="B85" t="n">
-        <v>57904</v>
+        <v>92561</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11522,10 +11521,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497625</v>
+        <v>497767</v>
       </c>
       <c r="R85" t="n">
-        <v>7040291</v>
+        <v>7040478</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11560,17 +11559,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11614,10 +11609,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889815</v>
+        <v>131889532</v>
       </c>
       <c r="B86" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11625,29 +11620,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -11657,10 +11651,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497472</v>
+        <v>497828</v>
       </c>
       <c r="R86" t="n">
-        <v>7040345</v>
+        <v>7040485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11695,17 +11689,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11714,11 +11704,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ86" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11729,9 +11714,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11749,10 +11739,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889818</v>
+        <v>131889868</v>
       </c>
       <c r="B87" t="n">
-        <v>57904</v>
+        <v>83112</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11760,31 +11750,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11792,10 +11777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497444</v>
+        <v>497696</v>
       </c>
       <c r="R87" t="n">
-        <v>7040224</v>
+        <v>7040335</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11830,17 +11815,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11884,10 +11865,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889532</v>
+        <v>131889540</v>
       </c>
       <c r="B88" t="n">
-        <v>91838</v>
+        <v>92137</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11895,21 +11876,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11926,10 +11907,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497828</v>
+        <v>497796</v>
       </c>
       <c r="R88" t="n">
-        <v>7040485</v>
+        <v>7040452</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11977,6 +11958,11 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12014,10 +12000,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889868</v>
+        <v>131889880</v>
       </c>
       <c r="B89" t="n">
-        <v>83112</v>
+        <v>89223</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12025,26 +12011,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12052,10 +12042,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497696</v>
+        <v>497791</v>
       </c>
       <c r="R89" t="n">
-        <v>7040335</v>
+        <v>7040457</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12120,9 +12110,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12140,10 +12135,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131889540</v>
+        <v>131889811</v>
       </c>
       <c r="B90" t="n">
-        <v>92137</v>
+        <v>57904</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12151,28 +12146,29 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -12182,10 +12178,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497796</v>
+        <v>497625</v>
       </c>
       <c r="R90" t="n">
-        <v>7040452</v>
+        <v>7040291</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12220,13 +12216,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12250,14 +12250,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12275,10 +12270,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131889880</v>
+        <v>131889815</v>
       </c>
       <c r="B91" t="n">
-        <v>89223</v>
+        <v>57904</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12286,28 +12281,29 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12317,10 +12313,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497791</v>
+        <v>497472</v>
       </c>
       <c r="R91" t="n">
-        <v>7040457</v>
+        <v>7040345</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12355,13 +12351,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12385,14 +12385,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12410,39 +12405,40 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131889795</v>
+        <v>131889818</v>
       </c>
       <c r="B92" t="n">
-        <v>92561</v>
+        <v>57904</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -12452,10 +12448,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497767</v>
+        <v>497444</v>
       </c>
       <c r="R92" t="n">
-        <v>7040478</v>
+        <v>7040224</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12490,13 +12486,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889777</v>
+        <v>131889827</v>
       </c>
       <c r="B105" t="n">
-        <v>83246</v>
+        <v>92137</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,26 +14088,30 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14115,10 +14119,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497473</v>
+        <v>497818</v>
       </c>
       <c r="R105" t="n">
-        <v>7040320</v>
+        <v>7040505</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14168,11 +14172,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14183,9 +14182,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14203,10 +14207,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889827</v>
+        <v>131889777</v>
       </c>
       <c r="B106" t="n">
-        <v>92137</v>
+        <v>83246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14214,30 +14218,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497818</v>
+        <v>497473</v>
       </c>
       <c r="R106" t="n">
-        <v>7040505</v>
+        <v>7040320</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14298,6 +14298,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14308,14 +14313,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -2893,10 +2893,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131889571</v>
+        <v>131888320</v>
       </c>
       <c r="B19" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497567</v>
+        <v>497822</v>
       </c>
       <c r="R19" t="n">
-        <v>7040434</v>
+        <v>7040565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,6 +2969,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på både döda och levande granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2984,11 +2989,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2999,9 +2999,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3019,10 +3024,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131888320</v>
+        <v>131889571</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3030,21 +3035,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497822</v>
+        <v>497567</v>
       </c>
       <c r="R20" t="n">
-        <v>7040565</v>
+        <v>7040434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,11 +3100,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på både döda och levande granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3115,6 +3115,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3125,14 +3130,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131889551</v>
+        <v>131888274</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3161,28 +3161,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3192,10 +3193,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497544</v>
+        <v>497820</v>
       </c>
       <c r="R21" t="n">
-        <v>7040208</v>
+        <v>7040580</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3230,24 +3231,23 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131889572</v>
+        <v>131889551</v>
       </c>
       <c r="B22" t="n">
-        <v>83112</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3291,26 +3291,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3318,10 +3322,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497575</v>
+        <v>497544</v>
       </c>
       <c r="R22" t="n">
-        <v>7040219</v>
+        <v>7040208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3386,14 +3390,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3411,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131888274</v>
+        <v>131889572</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>83112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3422,31 +3421,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3454,10 +3448,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497820</v>
+        <v>497575</v>
       </c>
       <c r="R23" t="n">
-        <v>7040580</v>
+        <v>7040219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3492,17 +3486,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3511,6 +3501,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3521,9 +3516,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888299</v>
+        <v>131888280</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>58063</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3808,41 +3808,50 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497547</v>
+        <v>497571</v>
       </c>
       <c r="R26" t="n">
-        <v>7040310</v>
+        <v>7040180</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3879,7 +3888,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3888,7 +3897,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3897,24 +3905,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3932,10 +3925,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888277</v>
+        <v>131888299</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3943,29 +3936,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3975,10 +3967,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497615</v>
+        <v>497547</v>
       </c>
       <c r="R27" t="n">
-        <v>7040285</v>
+        <v>7040310</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4015,7 +4007,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4024,6 +4016,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4042,9 +4035,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4454,10 +4452,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888280</v>
+        <v>131888277</v>
       </c>
       <c r="B31" t="n">
-        <v>58063</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4465,50 +4463,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497571</v>
+        <v>497615</v>
       </c>
       <c r="R31" t="n">
-        <v>7040180</v>
+        <v>7040285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4545,7 +4535,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4562,9 +4552,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -8086,41 +8086,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889796</v>
+        <v>131889526</v>
       </c>
       <c r="B59" t="n">
-        <v>92561</v>
+        <v>83246</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8128,10 +8124,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497619</v>
+        <v>497605</v>
       </c>
       <c r="R59" t="n">
-        <v>7040378</v>
+        <v>7040259</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8356,37 +8352,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889543</v>
+        <v>131889796</v>
       </c>
       <c r="B61" t="n">
-        <v>78278</v>
+        <v>92561</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497577</v>
+        <v>497619</v>
       </c>
       <c r="R61" t="n">
-        <v>7040217</v>
+        <v>7040378</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8482,10 +8482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889526</v>
+        <v>131889543</v>
       </c>
       <c r="B62" t="n">
-        <v>83246</v>
+        <v>78278</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8493,21 +8493,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497605</v>
+        <v>497577</v>
       </c>
       <c r="R62" t="n">
-        <v>7040259</v>
+        <v>7040217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -11479,32 +11479,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889795</v>
+        <v>131889532</v>
       </c>
       <c r="B85" t="n">
-        <v>92561</v>
+        <v>91838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497767</v>
+        <v>497828</v>
       </c>
       <c r="R85" t="n">
-        <v>7040478</v>
+        <v>7040485</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11574,11 +11574,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ85" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11589,9 +11584,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889532</v>
+        <v>131889868</v>
       </c>
       <c r="B86" t="n">
-        <v>91838</v>
+        <v>83112</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11620,30 +11620,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11651,10 +11647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497828</v>
+        <v>497696</v>
       </c>
       <c r="R86" t="n">
-        <v>7040485</v>
+        <v>7040335</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11704,6 +11700,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ86" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11714,14 +11715,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11739,10 +11735,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889868</v>
+        <v>131889540</v>
       </c>
       <c r="B87" t="n">
-        <v>83112</v>
+        <v>92137</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11750,26 +11746,30 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11777,10 +11777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497696</v>
+        <v>497796</v>
       </c>
       <c r="R87" t="n">
-        <v>7040335</v>
+        <v>7040452</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11845,9 +11845,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11865,10 +11870,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889540</v>
+        <v>131889880</v>
       </c>
       <c r="B88" t="n">
-        <v>92137</v>
+        <v>89223</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11876,21 +11881,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11907,10 +11912,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497796</v>
+        <v>497791</v>
       </c>
       <c r="R88" t="n">
-        <v>7040452</v>
+        <v>7040457</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12000,32 +12005,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889880</v>
+        <v>131889795</v>
       </c>
       <c r="B89" t="n">
-        <v>89223</v>
+        <v>92561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12042,10 +12047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497791</v>
+        <v>497767</v>
       </c>
       <c r="R89" t="n">
-        <v>7040457</v>
+        <v>7040478</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12110,14 +12115,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13305,10 +13305,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889805</v>
+        <v>131889881</v>
       </c>
       <c r="B99" t="n">
-        <v>57904</v>
+        <v>83238</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13316,31 +13316,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13348,10 +13343,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497802</v>
+        <v>497527</v>
       </c>
       <c r="R99" t="n">
-        <v>7040466</v>
+        <v>7040360</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13386,17 +13381,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13408,21 +13399,6 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13440,7 +13416,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131889806</v>
+        <v>131889805</v>
       </c>
       <c r="B100" t="n">
         <v>57904</v>
@@ -13483,10 +13459,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497569</v>
+        <v>497802</v>
       </c>
       <c r="R100" t="n">
-        <v>7040455</v>
+        <v>7040466</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13575,7 +13551,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131889819</v>
+        <v>131889806</v>
       </c>
       <c r="B101" t="n">
         <v>57904</v>
@@ -13618,10 +13594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497516</v>
+        <v>497569</v>
       </c>
       <c r="R101" t="n">
-        <v>7040136</v>
+        <v>7040455</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13710,10 +13686,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131889881</v>
+        <v>131889819</v>
       </c>
       <c r="B102" t="n">
-        <v>83238</v>
+        <v>57904</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13721,26 +13697,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13748,10 +13729,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497527</v>
+        <v>497516</v>
       </c>
       <c r="R102" t="n">
-        <v>7040360</v>
+        <v>7040136</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13786,13 +13767,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13804,6 +13789,21 @@
       <c r="AI102" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889827</v>
+        <v>131889777</v>
       </c>
       <c r="B105" t="n">
-        <v>92137</v>
+        <v>83246</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,30 +14088,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14119,10 +14115,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497818</v>
+        <v>497473</v>
       </c>
       <c r="R105" t="n">
-        <v>7040505</v>
+        <v>7040320</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14172,6 +14168,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14182,14 +14183,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14207,10 +14203,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889777</v>
+        <v>131889827</v>
       </c>
       <c r="B106" t="n">
-        <v>83246</v>
+        <v>92137</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14218,26 +14214,30 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497473</v>
+        <v>497818</v>
       </c>
       <c r="R106" t="n">
-        <v>7040320</v>
+        <v>7040505</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14298,11 +14298,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14313,9 +14308,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -2893,10 +2893,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131888320</v>
+        <v>131889571</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497822</v>
+        <v>497567</v>
       </c>
       <c r="R19" t="n">
-        <v>7040565</v>
+        <v>7040434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,11 +2969,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på både döda och levande granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2989,6 +2984,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2999,14 +2999,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3024,10 +3019,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131889571</v>
+        <v>131888320</v>
       </c>
       <c r="B20" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3035,21 +3030,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497567</v>
+        <v>497822</v>
       </c>
       <c r="R20" t="n">
-        <v>7040434</v>
+        <v>7040565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3100,6 +3095,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på både döda och levande granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3115,11 +3115,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3130,9 +3125,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131888274</v>
+        <v>131889551</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3161,29 +3161,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3193,10 +3192,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497820</v>
+        <v>497544</v>
       </c>
       <c r="R21" t="n">
-        <v>7040580</v>
+        <v>7040208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3231,23 +3230,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131889551</v>
+        <v>131889572</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>83112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3291,30 +3291,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3322,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497544</v>
+        <v>497575</v>
       </c>
       <c r="R22" t="n">
-        <v>7040208</v>
+        <v>7040219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3390,9 +3386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3411,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131889572</v>
+        <v>131888274</v>
       </c>
       <c r="B23" t="n">
-        <v>83112</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3421,26 +3422,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3448,10 +3454,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497575</v>
+        <v>497820</v>
       </c>
       <c r="R23" t="n">
-        <v>7040219</v>
+        <v>7040580</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3486,13 +3492,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3501,11 +3511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3516,14 +3521,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888280</v>
+        <v>131888299</v>
       </c>
       <c r="B26" t="n">
-        <v>58063</v>
+        <v>91834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3808,50 +3808,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497571</v>
+        <v>497547</v>
       </c>
       <c r="R26" t="n">
-        <v>7040180</v>
+        <v>7040310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3888,7 +3879,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3897,6 +3888,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3905,9 +3897,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3925,10 +3932,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888299</v>
+        <v>131888277</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3936,28 +3943,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3967,10 +3975,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497547</v>
+        <v>497615</v>
       </c>
       <c r="R27" t="n">
-        <v>7040310</v>
+        <v>7040285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4007,7 +4015,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4016,7 +4024,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4035,14 +4042,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4452,10 +4454,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888277</v>
+        <v>131888280</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>58063</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4463,42 +4465,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497615</v>
+        <v>497571</v>
       </c>
       <c r="R31" t="n">
-        <v>7040285</v>
+        <v>7040180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4535,7 +4545,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4552,19 +4562,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -8086,37 +8086,41 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889526</v>
+        <v>131889796</v>
       </c>
       <c r="B59" t="n">
-        <v>83246</v>
+        <v>92561</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8124,10 +8128,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497605</v>
+        <v>497619</v>
       </c>
       <c r="R59" t="n">
-        <v>7040259</v>
+        <v>7040378</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8352,41 +8356,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889796</v>
+        <v>131889543</v>
       </c>
       <c r="B61" t="n">
-        <v>92561</v>
+        <v>78278</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497619</v>
+        <v>497577</v>
       </c>
       <c r="R61" t="n">
-        <v>7040378</v>
+        <v>7040217</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8482,10 +8482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889543</v>
+        <v>131889526</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>83246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8493,21 +8493,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497577</v>
+        <v>497605</v>
       </c>
       <c r="R62" t="n">
-        <v>7040217</v>
+        <v>7040259</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -10572,10 +10572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889863</v>
+        <v>131889869</v>
       </c>
       <c r="B78" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497565</v>
+        <v>497732</v>
       </c>
       <c r="R78" t="n">
-        <v>7040468</v>
+        <v>7040316</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10646,11 +10646,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10703,10 +10698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889869</v>
+        <v>131889863</v>
       </c>
       <c r="B79" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10714,21 +10709,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10741,10 +10736,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497732</v>
+        <v>497565</v>
       </c>
       <c r="R79" t="n">
-        <v>7040316</v>
+        <v>7040468</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10777,6 +10772,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11479,32 +11479,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889532</v>
+        <v>131889795</v>
       </c>
       <c r="B85" t="n">
-        <v>91838</v>
+        <v>92561</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497828</v>
+        <v>497767</v>
       </c>
       <c r="R85" t="n">
-        <v>7040485</v>
+        <v>7040478</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11574,6 +11574,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ85" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11584,14 +11589,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889868</v>
+        <v>131889532</v>
       </c>
       <c r="B86" t="n">
-        <v>83112</v>
+        <v>91838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11620,26 +11620,30 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11647,10 +11651,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497696</v>
+        <v>497828</v>
       </c>
       <c r="R86" t="n">
-        <v>7040335</v>
+        <v>7040485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11700,11 +11704,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ86" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11715,9 +11714,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11735,10 +11739,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889540</v>
+        <v>131889868</v>
       </c>
       <c r="B87" t="n">
-        <v>92137</v>
+        <v>83112</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11746,30 +11750,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11777,10 +11777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497796</v>
+        <v>497696</v>
       </c>
       <c r="R87" t="n">
-        <v>7040452</v>
+        <v>7040335</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11845,14 +11845,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11870,10 +11865,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889880</v>
+        <v>131889540</v>
       </c>
       <c r="B88" t="n">
-        <v>89223</v>
+        <v>92137</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11881,21 +11876,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11912,10 +11907,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497791</v>
+        <v>497796</v>
       </c>
       <c r="R88" t="n">
-        <v>7040457</v>
+        <v>7040452</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12005,32 +12000,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889795</v>
+        <v>131889880</v>
       </c>
       <c r="B89" t="n">
-        <v>92561</v>
+        <v>89223</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12047,10 +12042,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497767</v>
+        <v>497791</v>
       </c>
       <c r="R89" t="n">
-        <v>7040478</v>
+        <v>7040457</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12115,9 +12110,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13305,10 +13305,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889881</v>
+        <v>131889805</v>
       </c>
       <c r="B99" t="n">
-        <v>83238</v>
+        <v>57904</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13316,26 +13316,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13343,10 +13348,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497527</v>
+        <v>497802</v>
       </c>
       <c r="R99" t="n">
-        <v>7040360</v>
+        <v>7040466</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13381,13 +13386,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13399,6 +13408,21 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13416,7 +13440,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131889805</v>
+        <v>131889806</v>
       </c>
       <c r="B100" t="n">
         <v>57904</v>
@@ -13459,10 +13483,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497802</v>
+        <v>497569</v>
       </c>
       <c r="R100" t="n">
-        <v>7040466</v>
+        <v>7040455</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13551,7 +13575,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131889806</v>
+        <v>131889819</v>
       </c>
       <c r="B101" t="n">
         <v>57904</v>
@@ -13594,10 +13618,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497569</v>
+        <v>497516</v>
       </c>
       <c r="R101" t="n">
-        <v>7040455</v>
+        <v>7040136</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13686,10 +13710,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131889819</v>
+        <v>131889881</v>
       </c>
       <c r="B102" t="n">
-        <v>57904</v>
+        <v>83238</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13697,31 +13721,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13729,10 +13748,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497516</v>
+        <v>497527</v>
       </c>
       <c r="R102" t="n">
-        <v>7040136</v>
+        <v>7040360</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13767,17 +13786,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -13789,21 +13804,6 @@
       <c r="AI102" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889777</v>
+        <v>131889827</v>
       </c>
       <c r="B105" t="n">
-        <v>83246</v>
+        <v>92137</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,26 +14088,30 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14115,10 +14119,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497473</v>
+        <v>497818</v>
       </c>
       <c r="R105" t="n">
-        <v>7040320</v>
+        <v>7040505</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14168,11 +14172,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14183,9 +14182,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14203,10 +14207,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889827</v>
+        <v>131889777</v>
       </c>
       <c r="B106" t="n">
-        <v>92137</v>
+        <v>83246</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14214,30 +14218,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497818</v>
+        <v>497473</v>
       </c>
       <c r="R106" t="n">
-        <v>7040505</v>
+        <v>7040320</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14298,6 +14298,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14308,14 +14313,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -1368,41 +1368,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888298</v>
+        <v>131888284</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>97909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1410,10 +1407,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497697</v>
+        <v>497516</v>
       </c>
       <c r="R7" t="n">
-        <v>7040367</v>
+        <v>7040157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1448,11 +1445,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1466,26 +1458,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1503,10 +1475,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888302</v>
+        <v>131888332</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,30 +1486,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,10 +1521,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497492</v>
+        <v>497456</v>
       </c>
       <c r="R8" t="n">
-        <v>7040191</v>
+        <v>7040270</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1583,6 +1559,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1608,14 +1589,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1633,7 +1609,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888332</v>
+        <v>131888324</v>
       </c>
       <c r="B9" t="n">
         <v>79266</v>
@@ -1661,16 +1637,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1679,10 +1647,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497456</v>
+        <v>497637</v>
       </c>
       <c r="R9" t="n">
-        <v>7040270</v>
+        <v>7040612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1719,7 +1687,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1767,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888324</v>
+        <v>131889559</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>91858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,26 +1746,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1805,10 +1773,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497637</v>
+        <v>497679</v>
       </c>
       <c r="R10" t="n">
-        <v>7040612</v>
+        <v>7040380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1841,11 +1809,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1893,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131889559</v>
+        <v>131888327</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,26 +1867,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1931,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497679</v>
+        <v>497615</v>
       </c>
       <c r="R11" t="n">
-        <v>7040380</v>
+        <v>7040418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1967,6 +1930,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2014,10 +1982,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888327</v>
+        <v>131888298</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,26 +1993,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2052,10 +2024,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497615</v>
+        <v>497697</v>
       </c>
       <c r="R12" t="n">
-        <v>7040418</v>
+        <v>7040367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,7 +2064,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2120,9 +2092,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2140,38 +2117,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888284</v>
+        <v>131888302</v>
       </c>
       <c r="B13" t="n">
-        <v>97909</v>
+        <v>91834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2179,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497516</v>
+        <v>497492</v>
       </c>
       <c r="R13" t="n">
-        <v>7040157</v>
+        <v>7040191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2230,6 +2210,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131889571</v>
+        <v>131888320</v>
       </c>
       <c r="B19" t="n">
-        <v>83112</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497567</v>
+        <v>497822</v>
       </c>
       <c r="R19" t="n">
-        <v>7040434</v>
+        <v>7040565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,6 +2969,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på både döda och levande granar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2984,11 +2989,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2999,9 +2999,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3019,10 +3024,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131888320</v>
+        <v>131889571</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>83112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3030,21 +3035,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3057,10 +3062,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497822</v>
+        <v>497567</v>
       </c>
       <c r="R20" t="n">
-        <v>7040565</v>
+        <v>7040434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,11 +3100,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på både döda och levande granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3115,6 +3115,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3125,14 +3130,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131889551</v>
+        <v>131888274</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3161,28 +3161,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3192,10 +3193,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497544</v>
+        <v>497820</v>
       </c>
       <c r="R21" t="n">
-        <v>7040208</v>
+        <v>7040580</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3230,24 +3231,23 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131889572</v>
+        <v>131889551</v>
       </c>
       <c r="B22" t="n">
-        <v>83112</v>
+        <v>91834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3291,26 +3291,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3318,10 +3322,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497575</v>
+        <v>497544</v>
       </c>
       <c r="R22" t="n">
-        <v>7040219</v>
+        <v>7040208</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3386,14 +3390,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3411,10 +3410,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131888274</v>
+        <v>131889572</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>83112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3422,31 +3421,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3454,10 +3448,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497820</v>
+        <v>497575</v>
       </c>
       <c r="R23" t="n">
-        <v>7040580</v>
+        <v>7040219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3492,17 +3486,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3511,6 +3501,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3521,9 +3516,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -8086,41 +8086,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889796</v>
+        <v>131889526</v>
       </c>
       <c r="B59" t="n">
-        <v>92561</v>
+        <v>83246</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8128,10 +8124,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497619</v>
+        <v>497605</v>
       </c>
       <c r="R59" t="n">
-        <v>7040378</v>
+        <v>7040259</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8356,37 +8352,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889543</v>
+        <v>131889796</v>
       </c>
       <c r="B61" t="n">
-        <v>78278</v>
+        <v>92561</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497577</v>
+        <v>497619</v>
       </c>
       <c r="R61" t="n">
-        <v>7040217</v>
+        <v>7040378</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8482,10 +8482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889526</v>
+        <v>131889543</v>
       </c>
       <c r="B62" t="n">
-        <v>83246</v>
+        <v>78278</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8493,21 +8493,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497605</v>
+        <v>497577</v>
       </c>
       <c r="R62" t="n">
-        <v>7040259</v>
+        <v>7040217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -9246,10 +9246,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889809</v>
+        <v>131889878</v>
       </c>
       <c r="B68" t="n">
-        <v>57904</v>
+        <v>83112</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9257,31 +9257,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497622</v>
+        <v>497559</v>
       </c>
       <c r="R68" t="n">
-        <v>7040347</v>
+        <v>7040336</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9327,17 +9322,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9381,10 +9372,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889804</v>
+        <v>131889834</v>
       </c>
       <c r="B69" t="n">
-        <v>57904</v>
+        <v>91834</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9392,29 +9383,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9424,10 +9414,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497834</v>
+        <v>497411</v>
       </c>
       <c r="R69" t="n">
-        <v>7040513</v>
+        <v>7040245</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9462,17 +9452,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9516,10 +9502,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889878</v>
+        <v>131889531</v>
       </c>
       <c r="B70" t="n">
-        <v>83112</v>
+        <v>91838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9527,26 +9513,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9554,10 +9544,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497559</v>
+        <v>497831</v>
       </c>
       <c r="R70" t="n">
-        <v>7040336</v>
+        <v>7040503</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9622,9 +9612,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9642,10 +9637,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889834</v>
+        <v>131889809</v>
       </c>
       <c r="B71" t="n">
-        <v>91834</v>
+        <v>57904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9653,28 +9648,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9684,10 +9680,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497411</v>
+        <v>497622</v>
       </c>
       <c r="R71" t="n">
-        <v>7040245</v>
+        <v>7040347</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9722,13 +9718,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889531</v>
+        <v>131889804</v>
       </c>
       <c r="B72" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9783,28 +9783,29 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9814,10 +9815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497831</v>
+        <v>497834</v>
       </c>
       <c r="R72" t="n">
-        <v>7040503</v>
+        <v>7040513</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9852,13 +9853,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9882,14 +9887,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -11479,32 +11479,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889795</v>
+        <v>131889532</v>
       </c>
       <c r="B85" t="n">
-        <v>92561</v>
+        <v>91838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497767</v>
+        <v>497828</v>
       </c>
       <c r="R85" t="n">
-        <v>7040478</v>
+        <v>7040485</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11574,11 +11574,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ85" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11589,9 +11584,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889532</v>
+        <v>131889868</v>
       </c>
       <c r="B86" t="n">
-        <v>91838</v>
+        <v>83112</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11620,30 +11620,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11651,10 +11647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497828</v>
+        <v>497696</v>
       </c>
       <c r="R86" t="n">
-        <v>7040485</v>
+        <v>7040335</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11704,6 +11700,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ86" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11714,14 +11715,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11739,10 +11735,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889868</v>
+        <v>131889540</v>
       </c>
       <c r="B87" t="n">
-        <v>83112</v>
+        <v>92137</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11750,26 +11746,30 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11777,10 +11777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497696</v>
+        <v>497796</v>
       </c>
       <c r="R87" t="n">
-        <v>7040335</v>
+        <v>7040452</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11845,9 +11845,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11865,10 +11870,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889540</v>
+        <v>131889880</v>
       </c>
       <c r="B88" t="n">
-        <v>92137</v>
+        <v>89223</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11876,21 +11881,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11907,10 +11912,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497796</v>
+        <v>497791</v>
       </c>
       <c r="R88" t="n">
-        <v>7040452</v>
+        <v>7040457</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -12000,32 +12005,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889880</v>
+        <v>131889795</v>
       </c>
       <c r="B89" t="n">
-        <v>89223</v>
+        <v>92561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -12042,10 +12047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497791</v>
+        <v>497767</v>
       </c>
       <c r="R89" t="n">
-        <v>7040457</v>
+        <v>7040478</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12110,14 +12115,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889827</v>
+        <v>131889777</v>
       </c>
       <c r="B105" t="n">
-        <v>92137</v>
+        <v>83246</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,30 +14088,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14119,10 +14115,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497818</v>
+        <v>497473</v>
       </c>
       <c r="R105" t="n">
-        <v>7040505</v>
+        <v>7040320</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14172,6 +14168,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14182,14 +14183,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14207,10 +14203,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889777</v>
+        <v>131889827</v>
       </c>
       <c r="B106" t="n">
-        <v>83246</v>
+        <v>92137</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14218,26 +14214,30 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14245,10 +14245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497473</v>
+        <v>497818</v>
       </c>
       <c r="R106" t="n">
-        <v>7040320</v>
+        <v>7040505</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14298,11 +14298,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14313,9 +14308,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131889552</v>
       </c>
       <c r="B2" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>131888330</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>131888333</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131888307</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>131888329</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>131888284</v>
       </c>
       <c r="B7" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>131888332</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>131888324</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>131889559</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>131888327</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>131888298</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>131888302</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>131888303</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>131888305</v>
       </c>
       <c r="B15" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>131888334</v>
       </c>
       <c r="B16" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>131888322</v>
       </c>
       <c r="B17" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>131888325</v>
       </c>
       <c r="B18" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131888320</v>
+        <v>131889571</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>83115</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497822</v>
+        <v>497567</v>
       </c>
       <c r="R19" t="n">
-        <v>7040565</v>
+        <v>7040434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2969,11 +2969,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på både döda och levande granar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2989,6 +2984,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2999,14 +2999,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3024,10 +3019,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131889571</v>
+        <v>131888320</v>
       </c>
       <c r="B20" t="n">
-        <v>83112</v>
+        <v>79269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3035,21 +3030,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3062,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497567</v>
+        <v>497822</v>
       </c>
       <c r="R20" t="n">
-        <v>7040434</v>
+        <v>7040565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3100,6 +3095,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på både döda och levande granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3115,11 +3115,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3130,9 +3125,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         <v>131888274</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>131889551</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>131889572</v>
       </c>
       <c r="B23" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>131889560</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>131888276</v>
       </c>
       <c r="B25" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888299</v>
+        <v>131888328</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>79269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3808,30 +3808,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3839,10 +3835,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497547</v>
+        <v>497707</v>
       </c>
       <c r="R26" t="n">
-        <v>7040310</v>
+        <v>7040362</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3879,7 +3875,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Riktigt på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3907,14 +3903,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3932,10 +3923,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888277</v>
+        <v>131889566</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3943,31 +3934,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3975,10 +3961,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497615</v>
+        <v>497620</v>
       </c>
       <c r="R27" t="n">
-        <v>7040285</v>
+        <v>7040526</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4015,7 +4001,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4024,12 +4010,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4062,10 +4054,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888328</v>
+        <v>131888277</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4073,26 +4065,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4100,10 +4097,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497707</v>
+        <v>497615</v>
       </c>
       <c r="R28" t="n">
-        <v>7040362</v>
+        <v>7040285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4140,7 +4137,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Riktigt på flera granar.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4149,7 +4146,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4191,7 +4187,7 @@
         <v>131888260</v>
       </c>
       <c r="B29" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4323,10 +4319,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131889566</v>
+        <v>131888299</v>
       </c>
       <c r="B30" t="n">
-        <v>79266</v>
+        <v>91837</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4334,26 +4330,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497620</v>
+        <v>497547</v>
       </c>
       <c r="R30" t="n">
-        <v>7040526</v>
+        <v>7040310</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4419,11 +4419,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4434,9 +4429,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4457,7 +4457,7 @@
         <v>131888280</v>
       </c>
       <c r="B31" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>131889550</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888319</v>
+        <v>131888273</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4723,34 +4723,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4758,10 +4755,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497795</v>
+        <v>497827</v>
       </c>
       <c r="R33" t="n">
-        <v>7040492</v>
+        <v>7040466</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4798,7 +4795,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på många granar.</t>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4807,7 +4804,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4828,12 +4824,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4851,10 +4847,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131889563</v>
+        <v>131888319</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4879,8 +4875,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4889,10 +4893,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497828</v>
+        <v>497795</v>
       </c>
       <c r="R34" t="n">
-        <v>7040520</v>
+        <v>7040492</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4957,9 +4961,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4977,10 +4986,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888326</v>
+        <v>131889563</v>
       </c>
       <c r="B35" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5015,10 +5024,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497550</v>
+        <v>497828</v>
       </c>
       <c r="R35" t="n">
-        <v>7040497</v>
+        <v>7040520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5055,7 +5064,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växer här på grenar av gamla grova granar med socklar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5083,14 +5092,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5108,10 +5112,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131889561</v>
+        <v>131888326</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>79269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5119,26 +5123,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5146,10 +5150,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497600</v>
+        <v>497550</v>
       </c>
       <c r="R36" t="n">
-        <v>7040262</v>
+        <v>7040497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5184,6 +5188,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer här på grenar av gamla grova granar med socklar.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5209,9 +5218,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5229,10 +5243,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131888273</v>
+        <v>131889561</v>
       </c>
       <c r="B37" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5240,29 +5254,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5272,10 +5281,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497827</v>
+        <v>497600</v>
       </c>
       <c r="R37" t="n">
-        <v>7040466</v>
+        <v>7040262</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5310,17 +5319,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5339,14 +5344,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5367,7 +5367,7 @@
         <v>131888331</v>
       </c>
       <c r="B38" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>131888282</v>
       </c>
       <c r="B39" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>131888300</v>
       </c>
       <c r="B40" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131889567</v>
+        <v>131888275</v>
       </c>
       <c r="B41" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5771,26 +5771,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5798,10 +5803,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497498</v>
+        <v>497763</v>
       </c>
       <c r="R41" t="n">
-        <v>7040214</v>
+        <v>7040580</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5838,7 +5843,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5847,7 +5852,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5856,11 +5860,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ41" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5873,12 +5872,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5896,10 +5895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131888321</v>
+        <v>131889567</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5926,11 +5925,7 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5938,10 +5933,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497767</v>
+        <v>497498</v>
       </c>
       <c r="R42" t="n">
-        <v>7040576</v>
+        <v>7040214</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5978,7 +5973,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Här finns fertila bålar med apothecier.</t>
+          <t>Rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5994,6 +5989,11 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6031,10 +6031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888304</v>
+        <v>131888321</v>
       </c>
       <c r="B43" t="n">
-        <v>91858</v>
+        <v>79269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6042,24 +6042,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6069,10 +6073,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497752</v>
+        <v>497767</v>
       </c>
       <c r="R43" t="n">
-        <v>7040566</v>
+        <v>7040576</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6107,6 +6111,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på flera granar. Här finns fertila bålar med apothecier.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6134,12 +6143,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6157,10 +6166,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888275</v>
+        <v>131888304</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6168,29 +6177,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6200,10 +6204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497763</v>
+        <v>497752</v>
       </c>
       <c r="R44" t="n">
-        <v>7040580</v>
+        <v>7040566</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6238,17 +6242,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>131888297</v>
       </c>
       <c r="B45" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>131889549</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>131888301</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131888323</v>
+        <v>131888278</v>
       </c>
       <c r="B48" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6688,26 +6688,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6715,10 +6720,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497679</v>
+        <v>497622</v>
       </c>
       <c r="R48" t="n">
-        <v>7040625</v>
+        <v>7040297</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6755,7 +6760,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6764,7 +6769,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6773,6 +6777,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6785,12 +6794,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6808,10 +6817,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131888278</v>
+        <v>131888323</v>
       </c>
       <c r="B49" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6819,31 +6828,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6851,10 +6855,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497622</v>
+        <v>497679</v>
       </c>
       <c r="R49" t="n">
-        <v>7040297</v>
+        <v>7040625</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6891,7 +6895,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6900,6 +6904,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6908,11 +6913,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
-        </is>
-      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6951,7 +6951,7 @@
         <v>131888259</v>
       </c>
       <c r="B50" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>131889565</v>
       </c>
       <c r="B51" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>131888306</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>131889883</v>
       </c>
       <c r="B53" t="n">
-        <v>83238</v>
+        <v>83241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>131889851</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>131889865</v>
       </c>
       <c r="B55" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>131889848</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>131889775</v>
       </c>
       <c r="B57" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>131889849</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889526</v>
+        <v>131889808</v>
       </c>
       <c r="B59" t="n">
-        <v>83246</v>
+        <v>57907</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8097,26 +8097,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8124,10 +8129,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497605</v>
+        <v>497512</v>
       </c>
       <c r="R59" t="n">
-        <v>7040259</v>
+        <v>7040418</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8162,13 +8167,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8192,9 +8201,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8212,10 +8226,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889808</v>
+        <v>131889526</v>
       </c>
       <c r="B60" t="n">
-        <v>57904</v>
+        <v>83249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8223,31 +8237,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8255,10 +8264,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497512</v>
+        <v>497605</v>
       </c>
       <c r="R60" t="n">
-        <v>7040418</v>
+        <v>7040259</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8293,17 +8302,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8327,14 +8332,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8355,7 +8355,7 @@
         <v>131889796</v>
       </c>
       <c r="B61" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>131889543</v>
       </c>
       <c r="B62" t="n">
-        <v>78278</v>
+        <v>78281</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131889829</v>
+        <v>131889807</v>
       </c>
       <c r="B63" t="n">
-        <v>78278</v>
+        <v>57907</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8619,26 +8619,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8646,10 +8651,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497561</v>
+        <v>497520</v>
       </c>
       <c r="R63" t="n">
-        <v>7040467</v>
+        <v>7040421</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8684,13 +8689,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8702,6 +8711,21 @@
       <c r="AI63" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8722,7 +8746,7 @@
         <v>131889776</v>
       </c>
       <c r="B64" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8845,10 +8869,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889807</v>
+        <v>131889829</v>
       </c>
       <c r="B65" t="n">
-        <v>57904</v>
+        <v>78281</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8856,31 +8880,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8888,10 +8907,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497520</v>
+        <v>497561</v>
       </c>
       <c r="R65" t="n">
-        <v>7040421</v>
+        <v>7040467</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8926,17 +8945,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8948,21 +8963,6 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8983,7 +8983,7 @@
         <v>131889816</v>
       </c>
       <c r="B66" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>131889855</v>
       </c>
       <c r="B67" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>131889878</v>
       </c>
       <c r="B68" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>131889834</v>
       </c>
       <c r="B69" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>131889531</v>
       </c>
       <c r="B70" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>131889809</v>
       </c>
       <c r="B71" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>131889804</v>
       </c>
       <c r="B72" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9907,32 +9907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889783</v>
+        <v>131889528</v>
       </c>
       <c r="B73" t="n">
-        <v>91838</v>
+        <v>91804</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497799</v>
+        <v>497610</v>
       </c>
       <c r="R73" t="n">
-        <v>7040466</v>
+        <v>7040287</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10042,10 +10042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889785</v>
+        <v>131889783</v>
       </c>
       <c r="B74" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497617</v>
+        <v>497799</v>
       </c>
       <c r="R74" t="n">
-        <v>7040562</v>
+        <v>7040466</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10144,17 +10144,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10172,10 +10177,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131889534</v>
+        <v>131889785</v>
       </c>
       <c r="B75" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10214,10 +10219,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497640</v>
+        <v>497617</v>
       </c>
       <c r="R75" t="n">
-        <v>7040232</v>
+        <v>7040562</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10267,19 +10272,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10297,32 +10307,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131889528</v>
+        <v>131889534</v>
       </c>
       <c r="B76" t="n">
-        <v>91801</v>
+        <v>91841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10339,10 +10349,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497610</v>
+        <v>497640</v>
       </c>
       <c r="R76" t="n">
-        <v>7040287</v>
+        <v>7040232</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10392,11 +10402,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ76" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10407,14 +10412,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10435,7 +10435,7 @@
         <v>131889810</v>
       </c>
       <c r="B77" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10572,10 +10572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889869</v>
+        <v>131889863</v>
       </c>
       <c r="B78" t="n">
-        <v>83112</v>
+        <v>79269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497732</v>
+        <v>497565</v>
       </c>
       <c r="R78" t="n">
-        <v>7040316</v>
+        <v>7040468</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10646,6 +10646,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10698,10 +10703,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889863</v>
+        <v>131889869</v>
       </c>
       <c r="B79" t="n">
-        <v>79266</v>
+        <v>83115</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10709,21 +10714,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10736,10 +10741,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497565</v>
+        <v>497732</v>
       </c>
       <c r="R79" t="n">
-        <v>7040468</v>
+        <v>7040316</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10772,11 +10777,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10832,7 +10832,7 @@
         <v>131889831</v>
       </c>
       <c r="B80" t="n">
-        <v>91834</v>
+        <v>91837</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>131889838</v>
       </c>
       <c r="B81" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>131889847</v>
       </c>
       <c r="B82" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11215,10 +11215,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131889789</v>
+        <v>131889866</v>
       </c>
       <c r="B83" t="n">
-        <v>91838</v>
+        <v>79269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11226,30 +11226,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11257,10 +11261,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497816</v>
+        <v>497516</v>
       </c>
       <c r="R83" t="n">
-        <v>7040474</v>
+        <v>7040148</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11295,6 +11299,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt!!</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11308,11 +11317,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11345,10 +11349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131889866</v>
+        <v>131889789</v>
       </c>
       <c r="B84" t="n">
-        <v>79266</v>
+        <v>91841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11356,34 +11360,30 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497516</v>
+        <v>497816</v>
       </c>
       <c r="R84" t="n">
-        <v>7040148</v>
+        <v>7040474</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11429,11 +11429,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt!!</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11447,6 +11442,11 @@
       <c r="AH84" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11479,10 +11479,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889532</v>
+        <v>131889815</v>
       </c>
       <c r="B85" t="n">
-        <v>91838</v>
+        <v>57907</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11490,28 +11490,29 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11521,10 +11522,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497828</v>
+        <v>497472</v>
       </c>
       <c r="R85" t="n">
-        <v>7040485</v>
+        <v>7040345</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11559,13 +11560,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11574,6 +11579,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ85" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11584,14 +11594,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11609,10 +11614,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889868</v>
+        <v>131889811</v>
       </c>
       <c r="B86" t="n">
-        <v>83112</v>
+        <v>57907</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11620,26 +11625,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -11647,10 +11657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497696</v>
+        <v>497625</v>
       </c>
       <c r="R86" t="n">
-        <v>7040335</v>
+        <v>7040291</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11685,13 +11695,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11735,10 +11749,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889540</v>
+        <v>131889818</v>
       </c>
       <c r="B87" t="n">
-        <v>92137</v>
+        <v>57907</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11746,28 +11760,29 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -11777,10 +11792,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497796</v>
+        <v>497444</v>
       </c>
       <c r="R87" t="n">
-        <v>7040452</v>
+        <v>7040224</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11815,13 +11830,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11845,14 +11864,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11870,10 +11884,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889880</v>
+        <v>131889532</v>
       </c>
       <c r="B88" t="n">
-        <v>89223</v>
+        <v>91841</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11881,21 +11895,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -11912,10 +11926,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497791</v>
+        <v>497828</v>
       </c>
       <c r="R88" t="n">
-        <v>7040457</v>
+        <v>7040485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11963,11 +11977,6 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12005,41 +12014,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889795</v>
+        <v>131889868</v>
       </c>
       <c r="B89" t="n">
-        <v>92561</v>
+        <v>83115</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12047,10 +12052,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497767</v>
+        <v>497696</v>
       </c>
       <c r="R89" t="n">
-        <v>7040478</v>
+        <v>7040335</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12135,10 +12140,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131889811</v>
+        <v>131889540</v>
       </c>
       <c r="B90" t="n">
-        <v>57904</v>
+        <v>92140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12146,29 +12151,28 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -12178,10 +12182,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497625</v>
+        <v>497796</v>
       </c>
       <c r="R90" t="n">
-        <v>7040291</v>
+        <v>7040452</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12216,17 +12220,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12250,9 +12250,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12270,40 +12275,39 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131889815</v>
+        <v>131889795</v>
       </c>
       <c r="B91" t="n">
-        <v>57904</v>
+        <v>92564</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12313,10 +12317,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497472</v>
+        <v>497767</v>
       </c>
       <c r="R91" t="n">
-        <v>7040345</v>
+        <v>7040478</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12351,17 +12355,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12405,10 +12405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131889818</v>
+        <v>131889880</v>
       </c>
       <c r="B92" t="n">
-        <v>57904</v>
+        <v>89226</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12416,29 +12416,28 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -12448,10 +12447,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497444</v>
+        <v>497791</v>
       </c>
       <c r="R92" t="n">
-        <v>7040224</v>
+        <v>7040457</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12486,17 +12485,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12520,9 +12515,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12540,52 +12540,61 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131889835</v>
+        <v>131889823</v>
       </c>
       <c r="B93" t="n">
-        <v>91834</v>
+        <v>57748</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1108</v>
+        <v>102621</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497549</v>
+        <v>497598</v>
       </c>
       <c r="R93" t="n">
-        <v>7040130</v>
+        <v>7040321</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12626,7 +12635,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12638,21 +12646,6 @@
       <c r="AI93" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12670,10 +12663,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131889533</v>
+        <v>131889835</v>
       </c>
       <c r="B94" t="n">
-        <v>91838</v>
+        <v>91837</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12681,21 +12674,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12712,10 +12705,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497784</v>
+        <v>497549</v>
       </c>
       <c r="R94" t="n">
-        <v>7040452</v>
+        <v>7040130</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12765,6 +12758,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ94" t="inlineStr">
         <is>
           <t>gran</t>
@@ -12775,14 +12773,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12800,61 +12793,52 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131889823</v>
+        <v>131889533</v>
       </c>
       <c r="B95" t="n">
-        <v>57745</v>
+        <v>91841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102621</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497598</v>
+        <v>497784</v>
       </c>
       <c r="R95" t="n">
-        <v>7040321</v>
+        <v>7040452</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12895,6 +12879,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12903,9 +12888,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131889786</v>
+        <v>131889853</v>
       </c>
       <c r="B96" t="n">
-        <v>91838</v>
+        <v>91861</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12934,23 +12934,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
@@ -12965,10 +12961,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497661</v>
+        <v>497592</v>
       </c>
       <c r="R96" t="n">
-        <v>7040289</v>
+        <v>7040180</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13053,10 +13049,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131889853</v>
+        <v>131889786</v>
       </c>
       <c r="B97" t="n">
-        <v>91858</v>
+        <v>91841</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13064,19 +13060,23 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -13091,10 +13091,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497592</v>
+        <v>497661</v>
       </c>
       <c r="R97" t="n">
-        <v>7040180</v>
+        <v>7040289</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13179,10 +13179,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131889852</v>
+        <v>131889805</v>
       </c>
       <c r="B98" t="n">
-        <v>91858</v>
+        <v>57907</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13190,24 +13190,29 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -13217,10 +13222,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497574</v>
+        <v>497802</v>
       </c>
       <c r="R98" t="n">
-        <v>7040148</v>
+        <v>7040466</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13255,13 +13260,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -13305,10 +13314,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889805</v>
+        <v>131889819</v>
       </c>
       <c r="B99" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13348,10 +13357,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497802</v>
+        <v>497516</v>
       </c>
       <c r="R99" t="n">
-        <v>7040466</v>
+        <v>7040136</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13443,7 +13452,7 @@
         <v>131889806</v>
       </c>
       <c r="B100" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13575,10 +13584,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131889819</v>
+        <v>131889852</v>
       </c>
       <c r="B101" t="n">
-        <v>57904</v>
+        <v>91861</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13586,29 +13595,24 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -13618,10 +13622,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497516</v>
+        <v>497574</v>
       </c>
       <c r="R101" t="n">
-        <v>7040136</v>
+        <v>7040148</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13656,17 +13660,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13710,10 +13710,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131889881</v>
+        <v>131889542</v>
       </c>
       <c r="B102" t="n">
-        <v>83238</v>
+        <v>78281</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13721,21 +13721,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13748,10 +13748,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497527</v>
+        <v>497686</v>
       </c>
       <c r="R102" t="n">
-        <v>7040360</v>
+        <v>7040411</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13801,9 +13801,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13821,10 +13831,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131889542</v>
+        <v>131889881</v>
       </c>
       <c r="B103" t="n">
-        <v>78278</v>
+        <v>83241</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13832,21 +13842,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -13859,10 +13869,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497686</v>
+        <v>497527</v>
       </c>
       <c r="R103" t="n">
-        <v>7040411</v>
+        <v>7040360</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13912,19 +13922,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13945,7 +13945,7 @@
         <v>131889817</v>
       </c>
       <c r="B104" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>131889777</v>
       </c>
       <c r="B105" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14203,10 +14203,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889827</v>
+        <v>131889525</v>
       </c>
       <c r="B106" t="n">
-        <v>92137</v>
+        <v>83249</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14214,30 +14214,26 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -14245,10 +14241,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497818</v>
+        <v>497570</v>
       </c>
       <c r="R106" t="n">
-        <v>7040505</v>
+        <v>7040437</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14298,6 +14294,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14308,14 +14309,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14333,10 +14329,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131889525</v>
+        <v>131889827</v>
       </c>
       <c r="B107" t="n">
-        <v>83246</v>
+        <v>92140</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14344,26 +14340,30 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14371,10 +14371,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497570</v>
+        <v>497818</v>
       </c>
       <c r="R107" t="n">
-        <v>7040437</v>
+        <v>7040505</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14424,11 +14424,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ107" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14439,9 +14434,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14462,7 +14462,7 @@
         <v>131889527</v>
       </c>
       <c r="B108" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>131889864</v>
       </c>
       <c r="B109" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14723,39 +14723,40 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131889797</v>
+        <v>131889813</v>
       </c>
       <c r="B110" t="n">
-        <v>92561</v>
+        <v>57907</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -14765,10 +14766,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497512</v>
+        <v>497538</v>
       </c>
       <c r="R110" t="n">
-        <v>7040344</v>
+        <v>7040327</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14803,19 +14804,28 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -14851,7 +14861,7 @@
         <v>131889778</v>
       </c>
       <c r="B111" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14977,7 +14987,7 @@
         <v>131889859</v>
       </c>
       <c r="B112" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15108,10 +15118,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131889813</v>
+        <v>131889784</v>
       </c>
       <c r="B113" t="n">
-        <v>57904</v>
+        <v>91841</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15119,29 +15129,28 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -15151,10 +15160,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497538</v>
+        <v>497693</v>
       </c>
       <c r="R113" t="n">
-        <v>7040327</v>
+        <v>7040594</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15189,17 +15198,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -15243,32 +15248,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131889784</v>
+        <v>131889797</v>
       </c>
       <c r="B114" t="n">
-        <v>91838</v>
+        <v>92564</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -15285,10 +15290,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497693</v>
+        <v>497512</v>
       </c>
       <c r="R114" t="n">
-        <v>7040594</v>
+        <v>7040344</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15336,11 +15341,6 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15376,7 +15376,7 @@
         <v>131889828</v>
       </c>
       <c r="B115" t="n">
-        <v>92221</v>
+        <v>92224</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15503,10 +15503,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131889839</v>
+        <v>131889814</v>
       </c>
       <c r="B116" t="n">
-        <v>91852</v>
+        <v>57907</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15514,28 +15514,29 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -15545,10 +15546,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497618</v>
+        <v>497490</v>
       </c>
       <c r="R116" t="n">
-        <v>7040361</v>
+        <v>7040364</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15583,13 +15584,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -15633,10 +15638,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131889814</v>
+        <v>131889839</v>
       </c>
       <c r="B117" t="n">
-        <v>57904</v>
+        <v>91855</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15644,29 +15649,28 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15676,10 +15680,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497490</v>
+        <v>497618</v>
       </c>
       <c r="R117" t="n">
-        <v>7040364</v>
+        <v>7040361</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15714,17 +15718,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15768,10 +15768,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131889882</v>
+        <v>131889850</v>
       </c>
       <c r="B118" t="n">
-        <v>83238</v>
+        <v>91861</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15779,26 +15779,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15806,10 +15806,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497616</v>
+        <v>497478</v>
       </c>
       <c r="R118" t="n">
-        <v>7040367</v>
+        <v>7040303</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15862,6 +15862,21 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15879,10 +15894,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131889836</v>
+        <v>131889882</v>
       </c>
       <c r="B119" t="n">
-        <v>91834</v>
+        <v>83241</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15890,30 +15905,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15921,10 +15932,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497587</v>
+        <v>497616</v>
       </c>
       <c r="R119" t="n">
-        <v>7040172</v>
+        <v>7040367</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15977,21 +15988,6 @@
       <c r="AI119" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16009,10 +16005,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131889850</v>
+        <v>131889836</v>
       </c>
       <c r="B120" t="n">
-        <v>91858</v>
+        <v>91837</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16020,19 +16016,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>497478</v>
+        <v>497587</v>
       </c>
       <c r="R120" t="n">
-        <v>7040303</v>
+        <v>7040172</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -16138,7 +16138,7 @@
         <v>131889812</v>
       </c>
       <c r="B121" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16270,10 +16270,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131889821</v>
+        <v>131889856</v>
       </c>
       <c r="B122" t="n">
-        <v>58063</v>
+        <v>91861</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16281,50 +16281,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>497547</v>
+        <v>497459</v>
       </c>
       <c r="R122" t="n">
-        <v>7040424</v>
+        <v>7040199</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16365,6 +16352,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -16373,9 +16361,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16393,10 +16391,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131889856</v>
+        <v>131889821</v>
       </c>
       <c r="B123" t="n">
-        <v>91858</v>
+        <v>58066</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16404,37 +16402,50 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>497459</v>
+        <v>497547</v>
       </c>
       <c r="R123" t="n">
-        <v>7040199</v>
+        <v>7040424</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16475,7 +16486,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -16484,19 +16494,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131889552</v>
       </c>
       <c r="B2" t="n">
-        <v>92215</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>131888330</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>131888333</v>
       </c>
       <c r="B4" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131888307</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>131888329</v>
       </c>
       <c r="B6" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1368,38 +1368,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888284</v>
+        <v>131888298</v>
       </c>
       <c r="B7" t="n">
-        <v>97912</v>
+        <v>91842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1407,10 +1410,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497516</v>
+        <v>497697</v>
       </c>
       <c r="R7" t="n">
-        <v>7040157</v>
+        <v>7040367</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1445,6 +1448,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1458,6 +1466,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1475,10 +1503,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888332</v>
+        <v>131888302</v>
       </c>
       <c r="B8" t="n">
-        <v>79269</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,34 +1514,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1521,10 +1545,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497456</v>
+        <v>497492</v>
       </c>
       <c r="R8" t="n">
-        <v>7040270</v>
+        <v>7040191</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1559,11 +1583,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1589,9 +1608,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,10 +1633,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888324</v>
+        <v>131888332</v>
       </c>
       <c r="B9" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,8 +1661,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1647,10 +1679,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497637</v>
+        <v>497456</v>
       </c>
       <c r="R9" t="n">
-        <v>7040612</v>
+        <v>7040270</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1719,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1735,10 +1767,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131889559</v>
+        <v>131888324</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>79274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1746,26 +1778,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1773,10 +1805,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497679</v>
+        <v>497637</v>
       </c>
       <c r="R10" t="n">
-        <v>7040380</v>
+        <v>7040612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,6 +1841,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1859,7 +1896,7 @@
         <v>131888327</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1982,10 +2019,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131888298</v>
+        <v>131889559</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>91866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,23 +2030,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -2024,10 +2057,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497697</v>
+        <v>497679</v>
       </c>
       <c r="R12" t="n">
-        <v>7040367</v>
+        <v>7040380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2062,11 +2095,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2092,14 +2120,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2117,41 +2140,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131888302</v>
+        <v>131888284</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>97917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2159,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497492</v>
+        <v>497516</v>
       </c>
       <c r="R13" t="n">
-        <v>7040191</v>
+        <v>7040157</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2210,26 +2230,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2247,65 +2247,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131888303</v>
+        <v>131888334</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497808</v>
+        <v>497584</v>
       </c>
       <c r="R14" t="n">
-        <v>7040518</v>
+        <v>7040177</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2340,12 +2323,18 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2354,9 +2343,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Naturskog dominerad av gran.</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2377,7 +2376,7 @@
         <v>131888305</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2510,48 +2509,65 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131888334</v>
+        <v>131888303</v>
       </c>
       <c r="B16" t="n">
-        <v>79269</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497584</v>
+        <v>497808</v>
       </c>
       <c r="R16" t="n">
-        <v>7040177</v>
+        <v>7040518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2586,18 +2602,12 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2606,19 +2616,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Naturskog dominerad av gran.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
         <v>131888322</v>
       </c>
       <c r="B17" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>131888325</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>131889571</v>
       </c>
       <c r="B19" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>131888320</v>
       </c>
       <c r="B20" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131888274</v>
+        <v>131889551</v>
       </c>
       <c r="B21" t="n">
-        <v>57907</v>
+        <v>91842</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3161,29 +3161,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3193,10 +3192,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497820</v>
+        <v>497544</v>
       </c>
       <c r="R21" t="n">
-        <v>7040580</v>
+        <v>7040208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3231,23 +3230,24 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131889551</v>
+        <v>131889572</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>83120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3291,30 +3291,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3322,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497544</v>
+        <v>497575</v>
       </c>
       <c r="R22" t="n">
-        <v>7040208</v>
+        <v>7040219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3390,9 +3386,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3410,10 +3411,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131889572</v>
+        <v>131888274</v>
       </c>
       <c r="B23" t="n">
-        <v>83115</v>
+        <v>57912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3421,26 +3422,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3448,10 +3454,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497575</v>
+        <v>497820</v>
       </c>
       <c r="R23" t="n">
-        <v>7040219</v>
+        <v>7040580</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3486,13 +3492,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3501,11 +3511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3516,14 +3521,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131889560</v>
+        <v>131888276</v>
       </c>
       <c r="B24" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3552,24 +3552,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497653</v>
+        <v>497590</v>
       </c>
       <c r="R24" t="n">
-        <v>7040280</v>
+        <v>7040459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3617,13 +3622,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3642,9 +3651,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3662,10 +3676,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131888276</v>
+        <v>131889560</v>
       </c>
       <c r="B25" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3673,29 +3687,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3705,10 +3714,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497590</v>
+        <v>497653</v>
       </c>
       <c r="R25" t="n">
-        <v>7040459</v>
+        <v>7040280</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3743,17 +3752,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3772,14 +3777,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888328</v>
+        <v>131888299</v>
       </c>
       <c r="B26" t="n">
-        <v>79269</v>
+        <v>91842</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3808,26 +3808,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3835,10 +3839,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497707</v>
+        <v>497547</v>
       </c>
       <c r="R26" t="n">
-        <v>7040362</v>
+        <v>7040310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3875,7 +3879,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Riktigt på flera granar.</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3903,9 +3907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3923,10 +3932,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131889566</v>
+        <v>131888277</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3934,26 +3943,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3961,10 +3975,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497620</v>
+        <v>497615</v>
       </c>
       <c r="R27" t="n">
-        <v>7040526</v>
+        <v>7040285</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4001,7 +4015,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4010,18 +4024,12 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4054,10 +4062,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888277</v>
+        <v>131888280</v>
       </c>
       <c r="B28" t="n">
-        <v>57907</v>
+        <v>58071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4065,42 +4073,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497615</v>
+        <v>497571</v>
       </c>
       <c r="R28" t="n">
-        <v>7040285</v>
+        <v>7040180</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4137,7 +4153,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4154,19 +4170,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4184,41 +4190,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131888260</v>
+        <v>131888328</v>
       </c>
       <c r="B29" t="n">
-        <v>92564</v>
+        <v>79274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4226,10 +4228,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497804</v>
+        <v>497707</v>
       </c>
       <c r="R29" t="n">
-        <v>7040465</v>
+        <v>7040362</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4266,7 +4268,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Fruktkroppar i en stående död gran.</t>
+          <t>Riktigt på flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4294,14 +4296,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4319,10 +4316,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131888299</v>
+        <v>131889566</v>
       </c>
       <c r="B30" t="n">
-        <v>91837</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4330,30 +4327,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4361,10 +4354,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497547</v>
+        <v>497620</v>
       </c>
       <c r="R30" t="n">
-        <v>7040310</v>
+        <v>7040526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4401,7 +4394,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4419,6 +4412,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4429,14 +4427,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4454,61 +4447,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888280</v>
+        <v>131888260</v>
       </c>
       <c r="B31" t="n">
-        <v>58066</v>
+        <v>92569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497571</v>
+        <v>497804</v>
       </c>
       <c r="R31" t="n">
-        <v>7040180</v>
+        <v>7040465</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4545,7 +4529,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
+          <t>Fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4554,6 +4538,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4562,9 +4547,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>131889550</v>
       </c>
       <c r="B32" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888273</v>
+        <v>131888319</v>
       </c>
       <c r="B33" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4723,31 +4723,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4755,10 +4758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497827</v>
+        <v>497795</v>
       </c>
       <c r="R33" t="n">
-        <v>7040466</v>
+        <v>7040492</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4795,7 +4798,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gränsen till färska, på en gran vid hyggeskanten.</t>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4804,6 +4807,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4824,12 +4828,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4847,10 +4851,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131888319</v>
+        <v>131889563</v>
       </c>
       <c r="B34" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4875,16 +4879,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4893,10 +4889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497795</v>
+        <v>497828</v>
       </c>
       <c r="R34" t="n">
-        <v>7040492</v>
+        <v>7040520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4933,7 +4929,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på många granar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4961,14 +4957,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4986,10 +4977,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131889563</v>
+        <v>131888326</v>
       </c>
       <c r="B35" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5024,10 +5015,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497828</v>
+        <v>497550</v>
       </c>
       <c r="R35" t="n">
-        <v>7040520</v>
+        <v>7040497</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5064,7 +5055,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Växer här på grenar av gamla grova granar med socklar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5092,9 +5083,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5112,10 +5108,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131888326</v>
+        <v>131889561</v>
       </c>
       <c r="B36" t="n">
-        <v>79269</v>
+        <v>91866</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5123,26 +5119,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5150,10 +5146,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497550</v>
+        <v>497600</v>
       </c>
       <c r="R36" t="n">
-        <v>7040497</v>
+        <v>7040262</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5188,11 +5184,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer här på grenar av gamla grova granar med socklar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5218,14 +5209,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5243,10 +5229,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131889561</v>
+        <v>131888273</v>
       </c>
       <c r="B37" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5254,24 +5240,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5281,10 +5272,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>497600</v>
+        <v>497827</v>
       </c>
       <c r="R37" t="n">
-        <v>7040262</v>
+        <v>7040466</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5319,13 +5310,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gränsen till färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5344,9 +5339,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5367,7 +5367,7 @@
         <v>131888331</v>
       </c>
       <c r="B38" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>131888282</v>
       </c>
       <c r="B39" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>131888300</v>
       </c>
       <c r="B40" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131888275</v>
+        <v>131889567</v>
       </c>
       <c r="B41" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5771,31 +5771,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5803,10 +5798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497763</v>
+        <v>497498</v>
       </c>
       <c r="R41" t="n">
-        <v>7040580</v>
+        <v>7040214</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5843,7 +5838,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Rikligt med garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5852,6 +5847,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5860,6 +5856,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ41" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5872,12 +5873,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5895,10 +5896,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131889567</v>
+        <v>131888321</v>
       </c>
       <c r="B42" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5925,7 +5926,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5933,10 +5938,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497498</v>
+        <v>497767</v>
       </c>
       <c r="R42" t="n">
-        <v>7040214</v>
+        <v>7040576</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5973,7 +5978,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar.</t>
+          <t>Rikligt med garnlav på flera granar. Här finns fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5989,11 +5994,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6031,10 +6031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888321</v>
+        <v>131888297</v>
       </c>
       <c r="B43" t="n">
-        <v>79269</v>
+        <v>91842</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6042,28 +6042,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497767</v>
+        <v>497565</v>
       </c>
       <c r="R43" t="n">
-        <v>7040576</v>
+        <v>7040502</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar. Här finns fertila bålar med apothecier.</t>
+          <t>I stambasen av en stående döende gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6141,14 +6141,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6166,10 +6161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131888304</v>
+        <v>131889549</v>
       </c>
       <c r="B44" t="n">
-        <v>91861</v>
+        <v>91842</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6177,19 +6172,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
@@ -6204,10 +6203,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497752</v>
+        <v>497841</v>
       </c>
       <c r="R44" t="n">
-        <v>7040566</v>
+        <v>7040484</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6267,14 +6266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6292,10 +6286,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131888297</v>
+        <v>131888301</v>
       </c>
       <c r="B45" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6334,10 +6328,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>497565</v>
+        <v>497499</v>
       </c>
       <c r="R45" t="n">
-        <v>7040502</v>
+        <v>7040192</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6374,7 +6368,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I stambasen av en stående döende gran.</t>
+          <t>I en stående döende gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6422,10 +6416,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131889549</v>
+        <v>131888304</v>
       </c>
       <c r="B46" t="n">
-        <v>91837</v>
+        <v>91866</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6433,23 +6427,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -6464,10 +6454,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497841</v>
+        <v>497752</v>
       </c>
       <c r="R46" t="n">
-        <v>7040484</v>
+        <v>7040566</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6527,9 +6517,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6547,10 +6542,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131888301</v>
+        <v>131888275</v>
       </c>
       <c r="B47" t="n">
-        <v>91837</v>
+        <v>57912</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6558,28 +6553,29 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6589,10 +6585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497499</v>
+        <v>497763</v>
       </c>
       <c r="R47" t="n">
-        <v>7040192</v>
+        <v>7040580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6629,7 +6625,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I en stående döende gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6638,7 +6634,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6657,9 +6652,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131888278</v>
+        <v>131888323</v>
       </c>
       <c r="B48" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6688,31 +6688,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6720,10 +6715,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497622</v>
+        <v>497679</v>
       </c>
       <c r="R48" t="n">
-        <v>7040297</v>
+        <v>7040625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6760,7 +6755,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6769,6 +6764,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6777,11 +6773,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6794,12 +6785,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6817,10 +6808,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131888323</v>
+        <v>131888278</v>
       </c>
       <c r="B49" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6828,26 +6819,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6855,10 +6851,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497679</v>
+        <v>497622</v>
       </c>
       <c r="R49" t="n">
-        <v>7040625</v>
+        <v>7040297</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6895,7 +6891,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6904,7 +6900,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6913,6 +6908,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
+        </is>
+      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6951,7 +6951,7 @@
         <v>131888259</v>
       </c>
       <c r="B50" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>131889565</v>
       </c>
       <c r="B51" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>131888306</v>
       </c>
       <c r="B52" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>131889883</v>
       </c>
       <c r="B53" t="n">
-        <v>83241</v>
+        <v>83246</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7456,10 +7456,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889851</v>
+        <v>131889865</v>
       </c>
       <c r="B54" t="n">
-        <v>91861</v>
+        <v>79274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7467,26 +7467,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7494,10 +7494,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497564</v>
+        <v>497474</v>
       </c>
       <c r="R54" t="n">
-        <v>7040145</v>
+        <v>7040328</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7532,6 +7532,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Mycket rikligt med garnlav här!!</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7545,6 +7550,11 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7577,10 +7587,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131889865</v>
+        <v>131889775</v>
       </c>
       <c r="B55" t="n">
-        <v>79269</v>
+        <v>83254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7588,21 +7598,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7615,10 +7625,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497474</v>
+        <v>497671</v>
       </c>
       <c r="R55" t="n">
-        <v>7040328</v>
+        <v>7040587</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7651,11 +7661,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Mycket rikligt med garnlav här!!</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7708,10 +7713,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131889848</v>
+        <v>131889851</v>
       </c>
       <c r="B56" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7746,10 +7751,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497679</v>
+        <v>497564</v>
       </c>
       <c r="R56" t="n">
-        <v>7040355</v>
+        <v>7040145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7797,11 +7802,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7834,10 +7834,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889775</v>
+        <v>131889848</v>
       </c>
       <c r="B57" t="n">
-        <v>83249</v>
+        <v>91866</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7845,26 +7845,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497671</v>
+        <v>497679</v>
       </c>
       <c r="R57" t="n">
-        <v>7040587</v>
+        <v>7040355</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>131889849</v>
       </c>
       <c r="B58" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8086,40 +8086,39 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889808</v>
+        <v>131889796</v>
       </c>
       <c r="B59" t="n">
-        <v>57907</v>
+        <v>92569</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8129,10 +8128,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497512</v>
+        <v>497619</v>
       </c>
       <c r="R59" t="n">
-        <v>7040418</v>
+        <v>7040378</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8167,17 +8166,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8201,14 +8196,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8226,10 +8216,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889526</v>
+        <v>131889543</v>
       </c>
       <c r="B60" t="n">
-        <v>83249</v>
+        <v>78286</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8237,21 +8227,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8264,10 +8254,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497605</v>
+        <v>497577</v>
       </c>
       <c r="R60" t="n">
-        <v>7040259</v>
+        <v>7040217</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8319,7 +8309,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -8352,41 +8342,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889796</v>
+        <v>131889526</v>
       </c>
       <c r="B61" t="n">
-        <v>92564</v>
+        <v>83254</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8394,10 +8380,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497619</v>
+        <v>497605</v>
       </c>
       <c r="R61" t="n">
-        <v>7040378</v>
+        <v>7040259</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8482,10 +8468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889543</v>
+        <v>131889808</v>
       </c>
       <c r="B62" t="n">
-        <v>78281</v>
+        <v>57912</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8493,26 +8479,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8520,10 +8511,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497577</v>
+        <v>497512</v>
       </c>
       <c r="R62" t="n">
-        <v>7040217</v>
+        <v>7040418</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8558,13 +8549,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8575,7 +8570,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8588,9 +8583,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131889807</v>
+        <v>131889829</v>
       </c>
       <c r="B63" t="n">
-        <v>57907</v>
+        <v>78286</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8619,31 +8619,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8651,10 +8646,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497520</v>
+        <v>497561</v>
       </c>
       <c r="R63" t="n">
-        <v>7040421</v>
+        <v>7040467</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8689,17 +8684,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8711,21 +8702,6 @@
       <c r="AI63" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8746,7 +8722,7 @@
         <v>131889776</v>
       </c>
       <c r="B64" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8869,10 +8845,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131889829</v>
+        <v>131889807</v>
       </c>
       <c r="B65" t="n">
-        <v>78281</v>
+        <v>57912</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8880,26 +8856,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8907,10 +8888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497561</v>
+        <v>497520</v>
       </c>
       <c r="R65" t="n">
-        <v>7040467</v>
+        <v>7040421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8945,13 +8926,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8963,6 +8948,21 @@
       <c r="AI65" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8980,10 +8980,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131889816</v>
+        <v>131889855</v>
       </c>
       <c r="B66" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8991,29 +8991,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9023,10 +9018,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497433</v>
+        <v>497671</v>
       </c>
       <c r="R66" t="n">
-        <v>7040274</v>
+        <v>7040299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -9061,17 +9056,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -9082,7 +9073,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9095,14 +9086,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9120,10 +9106,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131889855</v>
+        <v>131889816</v>
       </c>
       <c r="B67" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9131,24 +9117,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -9158,10 +9149,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497671</v>
+        <v>497433</v>
       </c>
       <c r="R67" t="n">
-        <v>7040299</v>
+        <v>7040274</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9196,13 +9187,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9213,7 +9208,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -9226,9 +9221,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9246,10 +9246,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889878</v>
+        <v>131889809</v>
       </c>
       <c r="B68" t="n">
-        <v>83115</v>
+        <v>57912</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9257,26 +9257,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497559</v>
+        <v>497622</v>
       </c>
       <c r="R68" t="n">
-        <v>7040336</v>
+        <v>7040347</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9322,13 +9327,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9372,10 +9381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889834</v>
+        <v>131889804</v>
       </c>
       <c r="B69" t="n">
-        <v>91837</v>
+        <v>57912</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9383,28 +9392,29 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9414,10 +9424,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497411</v>
+        <v>497834</v>
       </c>
       <c r="R69" t="n">
-        <v>7040245</v>
+        <v>7040513</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9452,13 +9462,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9502,10 +9516,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889531</v>
+        <v>131889878</v>
       </c>
       <c r="B70" t="n">
-        <v>91841</v>
+        <v>83120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9513,30 +9527,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9544,10 +9554,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497831</v>
+        <v>497559</v>
       </c>
       <c r="R70" t="n">
-        <v>7040503</v>
+        <v>7040336</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9612,14 +9622,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9637,10 +9642,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889809</v>
+        <v>131889834</v>
       </c>
       <c r="B71" t="n">
-        <v>57907</v>
+        <v>91842</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9648,29 +9653,28 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9680,10 +9684,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497622</v>
+        <v>497411</v>
       </c>
       <c r="R71" t="n">
-        <v>7040347</v>
+        <v>7040245</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9718,17 +9722,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889804</v>
+        <v>131889531</v>
       </c>
       <c r="B72" t="n">
-        <v>57907</v>
+        <v>91846</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9783,29 +9783,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9815,10 +9814,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497834</v>
+        <v>497831</v>
       </c>
       <c r="R72" t="n">
-        <v>7040513</v>
+        <v>7040503</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9853,17 +9852,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9887,9 +9882,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9907,32 +9907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889528</v>
+        <v>131889783</v>
       </c>
       <c r="B73" t="n">
-        <v>91804</v>
+        <v>91846</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497610</v>
+        <v>497799</v>
       </c>
       <c r="R73" t="n">
-        <v>7040287</v>
+        <v>7040466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10042,10 +10042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889783</v>
+        <v>131889785</v>
       </c>
       <c r="B74" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497799</v>
+        <v>497617</v>
       </c>
       <c r="R74" t="n">
-        <v>7040466</v>
+        <v>7040562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10144,22 +10144,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10177,10 +10172,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131889785</v>
+        <v>131889534</v>
       </c>
       <c r="B75" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10219,10 +10214,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497617</v>
+        <v>497640</v>
       </c>
       <c r="R75" t="n">
-        <v>7040562</v>
+        <v>7040232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10272,24 +10267,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10307,32 +10297,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131889534</v>
+        <v>131889528</v>
       </c>
       <c r="B76" t="n">
-        <v>91841</v>
+        <v>91809</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10349,10 +10339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497640</v>
+        <v>497610</v>
       </c>
       <c r="R76" t="n">
-        <v>7040232</v>
+        <v>7040287</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10402,6 +10392,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ76" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10412,9 +10407,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10435,7 +10435,7 @@
         <v>131889810</v>
       </c>
       <c r="B77" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10572,10 +10572,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131889863</v>
+        <v>131889869</v>
       </c>
       <c r="B78" t="n">
-        <v>79269</v>
+        <v>83120</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10583,21 +10583,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497565</v>
+        <v>497732</v>
       </c>
       <c r="R78" t="n">
-        <v>7040468</v>
+        <v>7040316</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10646,11 +10646,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10703,10 +10698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131889869</v>
+        <v>131889863</v>
       </c>
       <c r="B79" t="n">
-        <v>83115</v>
+        <v>79274</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10714,21 +10709,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -10741,10 +10736,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>497732</v>
+        <v>497565</v>
       </c>
       <c r="R79" t="n">
-        <v>7040316</v>
+        <v>7040468</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10777,6 +10772,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10832,7 +10832,7 @@
         <v>131889831</v>
       </c>
       <c r="B80" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>131889838</v>
       </c>
       <c r="B81" t="n">
-        <v>91855</v>
+        <v>91860</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>131889847</v>
       </c>
       <c r="B82" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11215,10 +11215,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131889866</v>
+        <v>131889789</v>
       </c>
       <c r="B83" t="n">
-        <v>79269</v>
+        <v>91846</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11226,34 +11226,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -11261,10 +11257,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497516</v>
+        <v>497816</v>
       </c>
       <c r="R83" t="n">
-        <v>7040148</v>
+        <v>7040474</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11299,11 +11295,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt!!</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -11317,6 +11308,11 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11349,10 +11345,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131889789</v>
+        <v>131889866</v>
       </c>
       <c r="B84" t="n">
-        <v>91841</v>
+        <v>79274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11360,30 +11356,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497816</v>
+        <v>497516</v>
       </c>
       <c r="R84" t="n">
-        <v>7040474</v>
+        <v>7040148</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11429,6 +11429,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt!!</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -11442,11 +11447,6 @@
       <c r="AH84" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -11479,10 +11479,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131889815</v>
+        <v>131889540</v>
       </c>
       <c r="B85" t="n">
-        <v>57907</v>
+        <v>92145</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11490,29 +11490,28 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11522,10 +11521,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>497472</v>
+        <v>497796</v>
       </c>
       <c r="R85" t="n">
-        <v>7040345</v>
+        <v>7040452</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11560,17 +11559,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11594,9 +11589,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -11614,10 +11614,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131889811</v>
+        <v>131889880</v>
       </c>
       <c r="B86" t="n">
-        <v>57907</v>
+        <v>89231</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11625,29 +11625,28 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -11657,10 +11656,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>497625</v>
+        <v>497791</v>
       </c>
       <c r="R86" t="n">
-        <v>7040291</v>
+        <v>7040457</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11695,17 +11694,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -11729,9 +11724,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131889818</v>
+        <v>131889532</v>
       </c>
       <c r="B87" t="n">
-        <v>57907</v>
+        <v>91846</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11760,29 +11760,28 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -11792,10 +11791,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497444</v>
+        <v>497828</v>
       </c>
       <c r="R87" t="n">
-        <v>7040224</v>
+        <v>7040485</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11830,17 +11829,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -11849,11 +11844,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ87" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11864,9 +11854,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -11884,10 +11879,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131889532</v>
+        <v>131889868</v>
       </c>
       <c r="B88" t="n">
-        <v>91841</v>
+        <v>83120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11895,30 +11890,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -11926,10 +11917,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497828</v>
+        <v>497696</v>
       </c>
       <c r="R88" t="n">
-        <v>7040485</v>
+        <v>7040335</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11979,6 +11970,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ88" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11989,14 +11985,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12014,37 +12005,41 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131889868</v>
+        <v>131889795</v>
       </c>
       <c r="B89" t="n">
-        <v>83115</v>
+        <v>92569</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12052,10 +12047,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497696</v>
+        <v>497767</v>
       </c>
       <c r="R89" t="n">
-        <v>7040335</v>
+        <v>7040478</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12140,10 +12135,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131889540</v>
+        <v>131889811</v>
       </c>
       <c r="B90" t="n">
-        <v>92140</v>
+        <v>57912</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12151,28 +12146,29 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -12182,10 +12178,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497796</v>
+        <v>497625</v>
       </c>
       <c r="R90" t="n">
-        <v>7040452</v>
+        <v>7040291</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12220,13 +12216,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12250,14 +12250,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12275,39 +12270,40 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131889795</v>
+        <v>131889815</v>
       </c>
       <c r="B91" t="n">
-        <v>92564</v>
+        <v>57912</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -12317,10 +12313,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497767</v>
+        <v>497472</v>
       </c>
       <c r="R91" t="n">
-        <v>7040478</v>
+        <v>7040345</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12355,13 +12351,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12405,10 +12405,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131889880</v>
+        <v>131889818</v>
       </c>
       <c r="B92" t="n">
-        <v>89226</v>
+        <v>57912</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12416,28 +12416,29 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -12447,10 +12448,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497791</v>
+        <v>497444</v>
       </c>
       <c r="R92" t="n">
-        <v>7040457</v>
+        <v>7040224</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12485,13 +12486,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -12515,14 +12520,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12543,7 +12543,7 @@
         <v>131889823</v>
       </c>
       <c r="B93" t="n">
-        <v>57748</v>
+        <v>57753</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>131889835</v>
       </c>
       <c r="B94" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>131889533</v>
       </c>
       <c r="B95" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131889853</v>
+        <v>131889786</v>
       </c>
       <c r="B96" t="n">
-        <v>91861</v>
+        <v>91846</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12934,19 +12934,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
@@ -12961,10 +12965,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>497592</v>
+        <v>497661</v>
       </c>
       <c r="R96" t="n">
-        <v>7040180</v>
+        <v>7040289</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -13049,10 +13053,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131889786</v>
+        <v>131889853</v>
       </c>
       <c r="B97" t="n">
-        <v>91841</v>
+        <v>91866</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13060,23 +13064,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
@@ -13091,10 +13091,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497661</v>
+        <v>497592</v>
       </c>
       <c r="R97" t="n">
-        <v>7040289</v>
+        <v>7040180</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13179,10 +13179,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131889805</v>
+        <v>131889542</v>
       </c>
       <c r="B98" t="n">
-        <v>57907</v>
+        <v>78286</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13190,31 +13190,26 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -13222,10 +13217,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497802</v>
+        <v>497686</v>
       </c>
       <c r="R98" t="n">
-        <v>7040466</v>
+        <v>7040411</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13260,28 +13255,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -13314,10 +13300,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889819</v>
+        <v>131889881</v>
       </c>
       <c r="B99" t="n">
-        <v>57907</v>
+        <v>83246</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13325,31 +13311,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13357,10 +13338,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497516</v>
+        <v>497527</v>
       </c>
       <c r="R99" t="n">
-        <v>7040136</v>
+        <v>7040360</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13395,17 +13376,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -13417,21 +13394,6 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13449,10 +13411,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131889806</v>
+        <v>131889852</v>
       </c>
       <c r="B100" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13460,29 +13422,24 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -13492,10 +13449,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497569</v>
+        <v>497574</v>
       </c>
       <c r="R100" t="n">
-        <v>7040455</v>
+        <v>7040148</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13530,17 +13487,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -13584,10 +13537,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131889852</v>
+        <v>131889805</v>
       </c>
       <c r="B101" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13595,24 +13548,29 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -13622,10 +13580,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497574</v>
+        <v>497802</v>
       </c>
       <c r="R101" t="n">
-        <v>7040148</v>
+        <v>7040466</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13660,13 +13618,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -13710,10 +13672,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131889542</v>
+        <v>131889806</v>
       </c>
       <c r="B102" t="n">
-        <v>78281</v>
+        <v>57912</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13721,26 +13683,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -13748,10 +13715,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>497686</v>
+        <v>497569</v>
       </c>
       <c r="R102" t="n">
-        <v>7040411</v>
+        <v>7040455</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13786,19 +13753,28 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -13831,10 +13807,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131889881</v>
+        <v>131889819</v>
       </c>
       <c r="B103" t="n">
-        <v>83241</v>
+        <v>57912</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13842,26 +13818,31 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13869,10 +13850,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497527</v>
+        <v>497516</v>
       </c>
       <c r="R103" t="n">
-        <v>7040360</v>
+        <v>7040136</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13907,13 +13888,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -13925,6 +13910,21 @@
       <c r="AI103" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13945,7 +13945,7 @@
         <v>131889817</v>
       </c>
       <c r="B104" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14077,10 +14077,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131889777</v>
+        <v>131889827</v>
       </c>
       <c r="B105" t="n">
-        <v>83249</v>
+        <v>92145</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14088,26 +14088,30 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -14115,10 +14119,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>497473</v>
+        <v>497818</v>
       </c>
       <c r="R105" t="n">
-        <v>7040320</v>
+        <v>7040505</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -14168,11 +14172,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14183,9 +14182,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -14203,10 +14207,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131889525</v>
+        <v>131889777</v>
       </c>
       <c r="B106" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14241,10 +14245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497570</v>
+        <v>497473</v>
       </c>
       <c r="R106" t="n">
-        <v>7040437</v>
+        <v>7040320</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14329,10 +14333,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131889827</v>
+        <v>131889525</v>
       </c>
       <c r="B107" t="n">
-        <v>92140</v>
+        <v>83254</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14340,30 +14344,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -14371,10 +14371,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497818</v>
+        <v>497570</v>
       </c>
       <c r="R107" t="n">
-        <v>7040505</v>
+        <v>7040437</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14424,6 +14424,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ107" t="inlineStr">
         <is>
           <t>gran</t>
@@ -14434,14 +14439,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -14462,7 +14462,7 @@
         <v>131889527</v>
       </c>
       <c r="B108" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>131889864</v>
       </c>
       <c r="B109" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14723,40 +14723,39 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131889813</v>
+        <v>131889797</v>
       </c>
       <c r="B110" t="n">
-        <v>57907</v>
+        <v>92569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -14766,10 +14765,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497538</v>
+        <v>497512</v>
       </c>
       <c r="R110" t="n">
-        <v>7040327</v>
+        <v>7040344</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14804,28 +14803,19 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -14858,37 +14848,42 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131889778</v>
+        <v>131889813</v>
       </c>
       <c r="B111" t="n">
-        <v>91804</v>
+        <v>57912</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -14896,10 +14891,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497523</v>
+        <v>497538</v>
       </c>
       <c r="R111" t="n">
-        <v>7040132</v>
+        <v>7040327</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14934,13 +14929,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -14984,10 +14983,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131889859</v>
+        <v>131889784</v>
       </c>
       <c r="B112" t="n">
-        <v>79269</v>
+        <v>91846</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14995,34 +14994,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -15030,10 +15025,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497784</v>
+        <v>497693</v>
       </c>
       <c r="R112" t="n">
-        <v>7040497</v>
+        <v>7040594</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15068,11 +15063,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Rikligt!! Flera särskilt långväxta bålar där en är över 70 cm lång.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -15086,6 +15076,11 @@
       <c r="AH112" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15118,32 +15113,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131889784</v>
+        <v>131889828</v>
       </c>
       <c r="B113" t="n">
-        <v>91841</v>
+        <v>92229</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15160,10 +15155,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497693</v>
+        <v>497800</v>
       </c>
       <c r="R113" t="n">
-        <v>7040594</v>
+        <v>7040458</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15248,10 +15243,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131889797</v>
+        <v>131889778</v>
       </c>
       <c r="B114" t="n">
-        <v>92564</v>
+        <v>91809</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15259,30 +15254,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -15290,10 +15281,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>497512</v>
+        <v>497523</v>
       </c>
       <c r="R114" t="n">
-        <v>7040344</v>
+        <v>7040132</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -15341,6 +15332,11 @@
       <c r="AH114" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -15373,41 +15369,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131889828</v>
+        <v>131889859</v>
       </c>
       <c r="B115" t="n">
-        <v>92224</v>
+        <v>79274</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15415,10 +15415,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497800</v>
+        <v>497784</v>
       </c>
       <c r="R115" t="n">
-        <v>7040458</v>
+        <v>7040497</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15453,6 +15453,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt!! Flera särskilt långväxta bålar där en är över 70 cm lång.</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -15466,11 +15471,6 @@
       <c r="AH115" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15506,7 +15506,7 @@
         <v>131889814</v>
       </c>
       <c r="B116" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>131889839</v>
       </c>
       <c r="B117" t="n">
-        <v>91855</v>
+        <v>91860</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15768,10 +15768,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131889850</v>
+        <v>131889882</v>
       </c>
       <c r="B118" t="n">
-        <v>91861</v>
+        <v>83246</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15779,26 +15779,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15806,10 +15806,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497478</v>
+        <v>497616</v>
       </c>
       <c r="R118" t="n">
-        <v>7040303</v>
+        <v>7040367</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15862,21 +15862,6 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15894,10 +15879,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131889882</v>
+        <v>131889850</v>
       </c>
       <c r="B119" t="n">
-        <v>83241</v>
+        <v>91866</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15905,26 +15890,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15932,10 +15917,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497616</v>
+        <v>497478</v>
       </c>
       <c r="R119" t="n">
-        <v>7040367</v>
+        <v>7040303</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15988,6 +15973,21 @@
       <c r="AI119" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16008,7 +16008,7 @@
         <v>131889836</v>
       </c>
       <c r="B120" t="n">
-        <v>91837</v>
+        <v>91842</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16135,10 +16135,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131889812</v>
+        <v>131889856</v>
       </c>
       <c r="B121" t="n">
-        <v>57907</v>
+        <v>91866</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16146,29 +16146,24 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -16178,10 +16173,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>497606</v>
+        <v>497459</v>
       </c>
       <c r="R121" t="n">
-        <v>7040301</v>
+        <v>7040199</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -16216,17 +16211,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -16235,24 +16226,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -16270,10 +16256,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131889856</v>
+        <v>131889812</v>
       </c>
       <c r="B122" t="n">
-        <v>91861</v>
+        <v>57912</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16281,24 +16267,29 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -16308,10 +16299,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>497459</v>
+        <v>497606</v>
       </c>
       <c r="R122" t="n">
-        <v>7040199</v>
+        <v>7040301</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -16346,13 +16337,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -16361,19 +16356,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -16394,7 +16394,7 @@
         <v>131889821</v>
       </c>
       <c r="B123" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131889552</v>
+        <v>131888330</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497603</v>
+        <v>497598</v>
       </c>
       <c r="R2" t="n">
-        <v>7040263</v>
+        <v>7040306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +761,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växer på gammal fruktkropp av granticka på en stubbe.</t>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,29 +779,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Naturskog med rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -815,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131888330</v>
+        <v>131888333</v>
       </c>
       <c r="B3" t="n">
         <v>79274</v>
@@ -845,7 +844,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497598</v>
+        <v>497455</v>
       </c>
       <c r="R3" t="n">
-        <v>7040306</v>
+        <v>7040215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på många granar.</t>
+          <t>Mycket rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131888333</v>
+        <v>131888307</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>91866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,34 +964,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1000,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497455</v>
+        <v>497644</v>
       </c>
       <c r="R4" t="n">
-        <v>7040215</v>
+        <v>7040292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1031,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket rikligt med garnlav på många granar.</t>
+          <t>Gott om fruktkroppar i en grov knäckt död gran med 42 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,6 +1049,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1070,12 +1066,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1093,30 +1089,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131888307</v>
+        <v>131889552</v>
       </c>
       <c r="B5" t="n">
-        <v>91866</v>
+        <v>92220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497644</v>
+        <v>497603</v>
       </c>
       <c r="R5" t="n">
-        <v>7040292</v>
+        <v>7040263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en grov knäckt död gran med 42 cm i brösthöjdsdiameter.</t>
+          <t>Växer på gammal fruktkropp av granticka på en stubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,27 +1191,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog med rikliga mängder död ved.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131888276</v>
+        <v>131889560</v>
       </c>
       <c r="B24" t="n">
-        <v>57912</v>
+        <v>91866</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3552,29 +3552,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497590</v>
+        <v>497653</v>
       </c>
       <c r="R24" t="n">
-        <v>7040459</v>
+        <v>7040280</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,17 +3617,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3651,14 +3642,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3676,10 +3662,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131889560</v>
+        <v>131888276</v>
       </c>
       <c r="B25" t="n">
-        <v>91866</v>
+        <v>57912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3687,24 +3673,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3714,10 +3705,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497653</v>
+        <v>497590</v>
       </c>
       <c r="R25" t="n">
-        <v>7040280</v>
+        <v>7040459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3752,13 +3743,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gammal bohål i grantickerötad granhögstubbe. Ev. skapat av tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3777,9 +3772,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888299</v>
+        <v>131888260</v>
       </c>
       <c r="B26" t="n">
-        <v>91842</v>
+        <v>92569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497547</v>
+        <v>497804</v>
       </c>
       <c r="R26" t="n">
-        <v>7040310</v>
+        <v>7040465</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888277</v>
+        <v>131888280</v>
       </c>
       <c r="B27" t="n">
-        <v>57912</v>
+        <v>58071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3943,42 +3943,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497615</v>
+        <v>497571</v>
       </c>
       <c r="R27" t="n">
-        <v>7040285</v>
+        <v>7040180</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4015,7 +4023,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4032,19 +4040,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4062,10 +4060,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888280</v>
+        <v>131888299</v>
       </c>
       <c r="B28" t="n">
-        <v>58071</v>
+        <v>91842</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4073,50 +4071,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497571</v>
+        <v>497547</v>
       </c>
       <c r="R28" t="n">
-        <v>7040180</v>
+        <v>7040310</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4153,7 +4142,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4162,6 +4151,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4170,9 +4160,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4447,39 +4452,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888260</v>
+        <v>131888277</v>
       </c>
       <c r="B31" t="n">
-        <v>92569</v>
+        <v>57912</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4489,10 +4495,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497804</v>
+        <v>497615</v>
       </c>
       <c r="R31" t="n">
-        <v>7040465</v>
+        <v>7040285</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4529,7 +4535,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Fruktkroppar i en stående död gran.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4538,7 +4544,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4557,14 +4562,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131888323</v>
+        <v>131888278</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6688,26 +6688,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6715,10 +6720,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497679</v>
+        <v>497622</v>
       </c>
       <c r="R48" t="n">
-        <v>7040625</v>
+        <v>7040297</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6755,7 +6760,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6764,7 +6769,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6773,6 +6777,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6785,12 +6794,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6808,10 +6817,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131888278</v>
+        <v>131888323</v>
       </c>
       <c r="B49" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6819,31 +6828,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6851,10 +6855,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497622</v>
+        <v>497679</v>
       </c>
       <c r="R49" t="n">
-        <v>7040297</v>
+        <v>7040625</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6891,7 +6895,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6900,6 +6904,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6908,11 +6913,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
-        </is>
-      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -8086,41 +8086,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889796</v>
+        <v>131889543</v>
       </c>
       <c r="B59" t="n">
-        <v>92569</v>
+        <v>78286</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8128,10 +8124,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497619</v>
+        <v>497577</v>
       </c>
       <c r="R59" t="n">
-        <v>7040378</v>
+        <v>7040217</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8183,7 +8179,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8216,37 +8212,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131889543</v>
+        <v>131889796</v>
       </c>
       <c r="B60" t="n">
-        <v>78286</v>
+        <v>92569</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>497577</v>
+        <v>497619</v>
       </c>
       <c r="R60" t="n">
-        <v>7040217</v>
+        <v>7040378</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -9246,10 +9246,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131889809</v>
+        <v>131889878</v>
       </c>
       <c r="B68" t="n">
-        <v>57912</v>
+        <v>83120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9257,31 +9257,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>497622</v>
+        <v>497559</v>
       </c>
       <c r="R68" t="n">
-        <v>7040347</v>
+        <v>7040336</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9327,17 +9322,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -9381,10 +9372,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889804</v>
+        <v>131889834</v>
       </c>
       <c r="B69" t="n">
-        <v>57912</v>
+        <v>91842</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9392,29 +9383,28 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9424,10 +9414,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497834</v>
+        <v>497411</v>
       </c>
       <c r="R69" t="n">
-        <v>7040513</v>
+        <v>7040245</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9462,17 +9452,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9516,10 +9502,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889878</v>
+        <v>131889531</v>
       </c>
       <c r="B70" t="n">
-        <v>83120</v>
+        <v>91846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9527,26 +9513,30 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9554,10 +9544,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497559</v>
+        <v>497831</v>
       </c>
       <c r="R70" t="n">
-        <v>7040336</v>
+        <v>7040503</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9622,9 +9612,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9642,10 +9637,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131889834</v>
+        <v>131889809</v>
       </c>
       <c r="B71" t="n">
-        <v>91842</v>
+        <v>57912</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9653,28 +9648,29 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9684,10 +9680,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>497411</v>
+        <v>497622</v>
       </c>
       <c r="R71" t="n">
-        <v>7040245</v>
+        <v>7040347</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9722,13 +9718,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9772,10 +9772,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131889531</v>
+        <v>131889804</v>
       </c>
       <c r="B72" t="n">
-        <v>91846</v>
+        <v>57912</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9783,28 +9783,29 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9814,10 +9815,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>497831</v>
+        <v>497834</v>
       </c>
       <c r="R72" t="n">
-        <v>7040503</v>
+        <v>7040513</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9852,13 +9853,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9882,14 +9887,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9907,32 +9907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889783</v>
+        <v>131889528</v>
       </c>
       <c r="B73" t="n">
-        <v>91846</v>
+        <v>91809</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497799</v>
+        <v>497610</v>
       </c>
       <c r="R73" t="n">
-        <v>7040466</v>
+        <v>7040287</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10042,10 +10042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889785</v>
+        <v>131889810</v>
       </c>
       <c r="B74" t="n">
-        <v>91846</v>
+        <v>57912</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10053,28 +10053,29 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10084,10 +10085,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497617</v>
+        <v>497721</v>
       </c>
       <c r="R74" t="n">
-        <v>7040562</v>
+        <v>7040314</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10122,13 +10123,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10144,17 +10149,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10172,7 +10182,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131889534</v>
+        <v>131889783</v>
       </c>
       <c r="B75" t="n">
         <v>91846</v>
@@ -10214,10 +10224,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497640</v>
+        <v>497799</v>
       </c>
       <c r="R75" t="n">
-        <v>7040232</v>
+        <v>7040466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10267,6 +10277,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ75" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10277,9 +10292,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10297,32 +10317,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131889528</v>
+        <v>131889785</v>
       </c>
       <c r="B76" t="n">
-        <v>91809</v>
+        <v>91846</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10339,10 +10359,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497610</v>
+        <v>497617</v>
       </c>
       <c r="R76" t="n">
-        <v>7040287</v>
+        <v>7040562</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10394,27 +10414,22 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10432,10 +10447,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889810</v>
+        <v>131889534</v>
       </c>
       <c r="B77" t="n">
-        <v>57912</v>
+        <v>91846</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10443,29 +10458,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10475,10 +10489,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497721</v>
+        <v>497640</v>
       </c>
       <c r="R77" t="n">
-        <v>7040314</v>
+        <v>7040232</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10513,17 +10527,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10532,11 +10542,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ77" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10547,14 +10552,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -15768,10 +15768,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131889882</v>
+        <v>131889836</v>
       </c>
       <c r="B118" t="n">
-        <v>83246</v>
+        <v>91842</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15779,26 +15779,30 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -15806,10 +15810,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>497616</v>
+        <v>497587</v>
       </c>
       <c r="R118" t="n">
-        <v>7040367</v>
+        <v>7040172</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15862,6 +15866,21 @@
       <c r="AI118" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -15879,10 +15898,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131889850</v>
+        <v>131889882</v>
       </c>
       <c r="B119" t="n">
-        <v>91866</v>
+        <v>83246</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15890,26 +15909,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -15917,10 +15936,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497478</v>
+        <v>497616</v>
       </c>
       <c r="R119" t="n">
-        <v>7040303</v>
+        <v>7040367</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15973,21 +15992,6 @@
       <c r="AI119" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -16005,10 +16009,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131889836</v>
+        <v>131889850</v>
       </c>
       <c r="B120" t="n">
-        <v>91842</v>
+        <v>91866</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16016,23 +16020,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>497587</v>
+        <v>497478</v>
       </c>
       <c r="R120" t="n">
-        <v>7040172</v>
+        <v>7040303</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 15659-2021 artfynd.xlsx
+++ b/artfynd/A 15659-2021 artfynd.xlsx
@@ -675,45 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131888330</v>
+        <v>131889552</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>92222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -721,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497598</v>
+        <v>497603</v>
       </c>
       <c r="R2" t="n">
-        <v>7040306</v>
+        <v>7040263</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på många granar.</t>
+          <t>Växer på gammal fruktkropp av granticka på en stubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,24 +775,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Naturskog med rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granticka</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Svamp, fruktkropp mm</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +815,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131888333</v>
+        <v>131888330</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,7 +845,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497455</v>
+        <v>497598</v>
       </c>
       <c r="R3" t="n">
-        <v>7040215</v>
+        <v>7040306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket rikligt med garnlav på många granar.</t>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -953,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131888307</v>
+        <v>131888333</v>
       </c>
       <c r="B4" t="n">
-        <v>91866</v>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,26 +965,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -991,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497644</v>
+        <v>497455</v>
       </c>
       <c r="R4" t="n">
-        <v>7040292</v>
+        <v>7040215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en grov knäckt död gran med 42 cm i brösthöjdsdiameter.</t>
+          <t>Mycket rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,11 +1058,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1066,12 +1070,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1089,34 +1093,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131889552</v>
+        <v>131888307</v>
       </c>
       <c r="B5" t="n">
-        <v>92220</v>
+        <v>91868</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497603</v>
+        <v>497644</v>
       </c>
       <c r="R5" t="n">
-        <v>7040263</v>
+        <v>7040292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på gammal fruktkropp av granticka på en stubbe.</t>
+          <t>Gott om fruktkroppar i en grov knäckt död gran med 42 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1191,27 +1191,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Naturskog med rikliga mängder död ved.</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>granticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Svamp, fruktkropp mm</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Fungi, fruit bodies, etc. # Porodaedalea chrysoloma s.lat.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
         <v>131888329</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131888298</v>
+        <v>131888332</v>
       </c>
       <c r="B7" t="n">
-        <v>91842</v>
+        <v>79276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,30 +1379,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1410,10 +1414,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497697</v>
+        <v>497456</v>
       </c>
       <c r="R7" t="n">
-        <v>7040367</v>
+        <v>7040270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1450,7 +1454,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,14 +1482,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1503,10 +1502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131888302</v>
+        <v>131888324</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,30 +1513,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,10 +1540,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497492</v>
+        <v>497637</v>
       </c>
       <c r="R8" t="n">
-        <v>7040191</v>
+        <v>7040612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1583,6 +1578,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1608,14 +1608,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1633,10 +1628,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131888332</v>
+        <v>131888327</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,16 +1656,8 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1679,10 +1666,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497456</v>
+        <v>497615</v>
       </c>
       <c r="R9" t="n">
-        <v>7040270</v>
+        <v>7040418</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1719,7 +1706,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1767,10 +1754,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131888324</v>
+        <v>131889559</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>91868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1778,26 +1765,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1805,10 +1792,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497637</v>
+        <v>497679</v>
       </c>
       <c r="R10" t="n">
-        <v>7040612</v>
+        <v>7040380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1841,11 +1828,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1893,10 +1875,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131888327</v>
+        <v>131888298</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>91844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1904,26 +1886,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1931,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497615</v>
+        <v>497697</v>
       </c>
       <c r="R11" t="n">
-        <v>7040418</v>
+        <v>7040367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1971,7 +1957,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1999,9 +1985,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2019,10 +2010,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131889559</v>
+        <v>131888302</v>
       </c>
       <c r="B12" t="n">
-        <v>91866</v>
+        <v>91844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,19 +2021,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
@@ -2057,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497679</v>
+        <v>497492</v>
       </c>
       <c r="R12" t="n">
-        <v>7040380</v>
+        <v>7040191</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2120,9 +2115,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2143,7 +2143,7 @@
         <v>131888284</v>
       </c>
       <c r="B13" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131888334</v>
+        <v>131888305</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>91868</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2258,26 +2258,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497584</v>
+        <v>497587</v>
       </c>
       <c r="R14" t="n">
-        <v>7040177</v>
+        <v>7040459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Många fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2343,6 +2343,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2353,9 +2358,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2373,10 +2383,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131888305</v>
+        <v>131888334</v>
       </c>
       <c r="B15" t="n">
-        <v>91866</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2384,26 +2394,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2411,10 +2421,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497587</v>
+        <v>497584</v>
       </c>
       <c r="R15" t="n">
-        <v>7040459</v>
+        <v>7040177</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2451,7 +2461,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Många fruktkroppar i en granhögstubbe.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2469,11 +2479,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
-        </is>
-      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2484,14 +2489,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
         <v>131888303</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57906</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>131888322</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>131888325</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>131889571</v>
       </c>
       <c r="B19" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>131888320</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>131889551</v>
       </c>
       <c r="B21" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>131889572</v>
       </c>
       <c r="B22" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>131888274</v>
       </c>
       <c r="B23" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>131889560</v>
       </c>
       <c r="B24" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>131888276</v>
       </c>
       <c r="B25" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131888260</v>
+        <v>131888299</v>
       </c>
       <c r="B26" t="n">
-        <v>92569</v>
+        <v>91844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497804</v>
+        <v>497547</v>
       </c>
       <c r="R26" t="n">
-        <v>7040465</v>
+        <v>7040310</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fruktkroppar i en stående död gran.</t>
+          <t>I stående död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131888280</v>
+        <v>131888328</v>
       </c>
       <c r="B27" t="n">
-        <v>58071</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3943,50 +3943,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>497571</v>
+        <v>497707</v>
       </c>
       <c r="R27" t="n">
-        <v>7040180</v>
+        <v>7040362</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4023,7 +4010,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
+          <t>Riktigt på flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4032,6 +4019,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4040,9 +4028,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4060,10 +4058,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131888299</v>
+        <v>131889566</v>
       </c>
       <c r="B28" t="n">
-        <v>91842</v>
+        <v>79276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4071,30 +4069,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4102,10 +4096,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>497547</v>
+        <v>497620</v>
       </c>
       <c r="R28" t="n">
-        <v>7040310</v>
+        <v>7040526</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4142,7 +4136,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I stående död gran.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4160,6 +4154,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4170,14 +4169,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4195,37 +4189,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131888328</v>
+        <v>131888260</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>92571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4233,10 +4231,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>497707</v>
+        <v>497804</v>
       </c>
       <c r="R29" t="n">
-        <v>7040362</v>
+        <v>7040465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4273,7 +4271,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Riktigt på flera granar.</t>
+          <t>Fruktkroppar i en stående död gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4301,9 +4299,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4321,10 +4324,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131889566</v>
+        <v>131888277</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4332,26 +4335,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4359,10 +4367,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497620</v>
+        <v>497615</v>
       </c>
       <c r="R30" t="n">
-        <v>7040526</v>
+        <v>7040285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4399,7 +4407,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4408,18 +4416,12 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4452,10 +4454,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131888277</v>
+        <v>131888280</v>
       </c>
       <c r="B31" t="n">
-        <v>57912</v>
+        <v>58073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4463,42 +4465,50 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497615</v>
+        <v>497571</v>
       </c>
       <c r="R31" t="n">
-        <v>7040285</v>
+        <v>7040180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4535,7 +4545,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Fyndplatsen finns i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4552,19 +4562,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>131889550</v>
       </c>
       <c r="B32" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131888319</v>
+        <v>131889561</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>91868</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4723,34 +4723,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4758,10 +4750,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>497795</v>
+        <v>497600</v>
       </c>
       <c r="R33" t="n">
-        <v>7040492</v>
+        <v>7040262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4796,11 +4788,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på många granar.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4826,14 +4813,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4851,10 +4833,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131889563</v>
+        <v>131888319</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4879,8 +4861,16 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4889,10 +4879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>497828</v>
+        <v>497795</v>
       </c>
       <c r="R34" t="n">
-        <v>7040520</v>
+        <v>7040492</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4929,7 +4919,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4957,9 +4947,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4977,10 +4972,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131888326</v>
+        <v>131889563</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5015,10 +5010,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>497550</v>
+        <v>497828</v>
       </c>
       <c r="R35" t="n">
-        <v>7040497</v>
+        <v>7040520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5055,7 +5050,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växer här på grenar av gamla grova granar med socklar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5083,14 +5078,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5108,10 +5098,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131889561</v>
+        <v>131888326</v>
       </c>
       <c r="B36" t="n">
-        <v>91866</v>
+        <v>79276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5119,26 +5109,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5146,10 +5136,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>497600</v>
+        <v>497550</v>
       </c>
       <c r="R36" t="n">
-        <v>7040262</v>
+        <v>7040497</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5184,6 +5174,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer här på grenar av gamla grova granar med socklar.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5209,9 +5204,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5232,7 +5232,7 @@
         <v>131888273</v>
       </c>
       <c r="B37" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>131888331</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>131888282</v>
       </c>
       <c r="B39" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>131888300</v>
       </c>
       <c r="B40" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>131889567</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>131888321</v>
       </c>
       <c r="B42" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131888297</v>
+        <v>131888304</v>
       </c>
       <c r="B43" t="n">
-        <v>91842</v>
+        <v>91868</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6042,23 +6042,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
@@ -6073,10 +6069,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497565</v>
+        <v>497752</v>
       </c>
       <c r="R43" t="n">
-        <v>7040502</v>
+        <v>7040566</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6111,11 +6107,6 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I stambasen av en stående döende gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6141,9 +6132,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6161,10 +6157,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131889549</v>
+        <v>131888275</v>
       </c>
       <c r="B44" t="n">
-        <v>91842</v>
+        <v>57914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6172,28 +6168,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6203,10 +6200,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497841</v>
+        <v>497763</v>
       </c>
       <c r="R44" t="n">
-        <v>7040484</v>
+        <v>7040580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6241,13 +6238,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6266,9 +6267,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6289,7 +6295,7 @@
         <v>131888301</v>
       </c>
       <c r="B45" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6416,10 +6422,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131888304</v>
+        <v>131888297</v>
       </c>
       <c r="B46" t="n">
-        <v>91866</v>
+        <v>91844</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6427,19 +6433,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
@@ -6454,10 +6464,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497752</v>
+        <v>497565</v>
       </c>
       <c r="R46" t="n">
-        <v>7040566</v>
+        <v>7040502</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6492,6 +6502,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I stambasen av en stående döende gran.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6517,14 +6532,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6542,10 +6552,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131888275</v>
+        <v>131889549</v>
       </c>
       <c r="B47" t="n">
-        <v>57912</v>
+        <v>91844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6553,29 +6563,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6585,10 +6594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497763</v>
+        <v>497841</v>
       </c>
       <c r="R47" t="n">
-        <v>7040580</v>
+        <v>7040484</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6623,17 +6632,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6652,14 +6657,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131888278</v>
+        <v>131888323</v>
       </c>
       <c r="B48" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6688,31 +6688,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6720,10 +6715,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497622</v>
+        <v>497679</v>
       </c>
       <c r="R48" t="n">
-        <v>7040297</v>
+        <v>7040625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6760,7 +6755,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6769,6 +6764,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6777,11 +6773,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6794,12 +6785,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6817,10 +6808,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131888323</v>
+        <v>131888278</v>
       </c>
       <c r="B49" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6828,26 +6819,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6855,10 +6851,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497679</v>
+        <v>497622</v>
       </c>
       <c r="R49" t="n">
-        <v>7040625</v>
+        <v>7040297</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6895,7 +6891,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Riktigt med garnlav på både döda och levande stående granar.</t>
+          <t>Ringhack, färska, i riklig mängd på en gran med spår av kådaflöde. Mycket högt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6904,7 +6900,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6913,6 +6908,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Naturskog med stora mängder stående död granved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett i stora delar av ytan.</t>
+        </is>
+      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6951,7 +6951,7 @@
         <v>131888259</v>
       </c>
       <c r="B50" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>131889565</v>
       </c>
       <c r="B51" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>131888306</v>
       </c>
       <c r="B52" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7345,10 +7345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131889883</v>
+        <v>131889865</v>
       </c>
       <c r="B53" t="n">
-        <v>83246</v>
+        <v>79276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7356,21 +7356,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497621</v>
+        <v>497474</v>
       </c>
       <c r="R53" t="n">
-        <v>7040366</v>
+        <v>7040328</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7421,6 +7421,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mycket rikligt med garnlav här!!</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7439,6 +7444,21 @@
       <c r="AI53" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7456,10 +7476,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131889865</v>
+        <v>131889775</v>
       </c>
       <c r="B54" t="n">
-        <v>79274</v>
+        <v>83256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7467,21 +7487,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7494,10 +7514,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497474</v>
+        <v>497671</v>
       </c>
       <c r="R54" t="n">
-        <v>7040328</v>
+        <v>7040587</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7530,11 +7550,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Mycket rikligt med garnlav här!!</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7587,10 +7602,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131889775</v>
+        <v>131889851</v>
       </c>
       <c r="B55" t="n">
-        <v>83254</v>
+        <v>91868</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7598,26 +7613,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7625,10 +7640,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497671</v>
+        <v>497564</v>
       </c>
       <c r="R55" t="n">
-        <v>7040587</v>
+        <v>7040145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7676,11 +7691,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7713,10 +7723,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131889851</v>
+        <v>131889848</v>
       </c>
       <c r="B56" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7751,10 +7761,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497564</v>
+        <v>497679</v>
       </c>
       <c r="R56" t="n">
-        <v>7040145</v>
+        <v>7040355</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7802,6 +7812,11 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7834,10 +7849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131889848</v>
+        <v>131889849</v>
       </c>
       <c r="B57" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7875,7 +7890,7 @@
         <v>497679</v>
       </c>
       <c r="R57" t="n">
-        <v>7040355</v>
+        <v>7040341</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7960,10 +7975,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131889849</v>
+        <v>131889883</v>
       </c>
       <c r="B58" t="n">
-        <v>91866</v>
+        <v>83248</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7971,26 +7986,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7998,10 +8013,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497679</v>
+        <v>497621</v>
       </c>
       <c r="R58" t="n">
-        <v>7040341</v>
+        <v>7040366</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8054,21 +8069,6 @@
       <c r="AI58" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131889543</v>
+        <v>131889526</v>
       </c>
       <c r="B59" t="n">
-        <v>78286</v>
+        <v>83256</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8097,21 +8097,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8124,10 +8124,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>497577</v>
+        <v>497605</v>
       </c>
       <c r="R59" t="n">
-        <v>7040217</v>
+        <v>7040259</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8215,7 +8215,7 @@
         <v>131889796</v>
       </c>
       <c r="B60" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131889526</v>
+        <v>131889808</v>
       </c>
       <c r="B61" t="n">
-        <v>83254</v>
+        <v>57914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8353,26 +8353,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8380,10 +8385,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>497605</v>
+        <v>497512</v>
       </c>
       <c r="R61" t="n">
-        <v>7040259</v>
+        <v>7040418</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8418,13 +8423,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8448,9 +8457,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8468,10 +8482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131889808</v>
+        <v>131889543</v>
       </c>
       <c r="B62" t="n">
-        <v>57912</v>
+        <v>78288</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8479,31 +8493,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8511,10 +8520,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>497512</v>
+        <v>497577</v>
       </c>
       <c r="R62" t="n">
-        <v>7040418</v>
+        <v>7040217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8549,17 +8558,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8570,7 +8575,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -8583,14 +8588,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131889829</v>
+        <v>131889776</v>
       </c>
       <c r="B63" t="n">
-        <v>78286</v>
+        <v>83256</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8619,21 +8619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>497561</v>
+        <v>497530</v>
       </c>
       <c r="R63" t="n">
-        <v>7040467</v>
+        <v>7040312</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8702,6 +8702,21 @@
       <c r="AI63" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8719,10 +8734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131889776</v>
+        <v>131889829</v>
       </c>
       <c r="B64" t="n">
-        <v>83254</v>
+        <v>78288</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8730,21 +8745,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8757,10 +8772,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497530</v>
+        <v>497561</v>
       </c>
       <c r="R64" t="n">
-        <v>7040312</v>
+        <v>7040467</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8813,21 +8828,6 @@
       <c r="AI64" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8848,7 +8848,7 @@
         <v>131889807</v>
       </c>
       <c r="B65" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>131889855</v>
       </c>
       <c r="B66" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>131889816</v>
       </c>
       <c r="B67" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>131889878</v>
       </c>
       <c r="B68" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9372,10 +9372,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131889834</v>
+        <v>131889531</v>
       </c>
       <c r="B69" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9383,21 +9383,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9414,10 +9414,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>497411</v>
+        <v>497831</v>
       </c>
       <c r="R69" t="n">
-        <v>7040245</v>
+        <v>7040503</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9482,9 +9482,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9502,10 +9507,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131889531</v>
+        <v>131889834</v>
       </c>
       <c r="B70" t="n">
-        <v>91846</v>
+        <v>91844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9513,21 +9518,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9544,10 +9549,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>497831</v>
+        <v>497411</v>
       </c>
       <c r="R70" t="n">
-        <v>7040503</v>
+        <v>7040245</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9612,14 +9617,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9640,7 +9640,7 @@
         <v>131889809</v>
       </c>
       <c r="B71" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>131889804</v>
       </c>
       <c r="B72" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9907,32 +9907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131889528</v>
+        <v>131889783</v>
       </c>
       <c r="B73" t="n">
-        <v>91809</v>
+        <v>91848</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>497610</v>
+        <v>497799</v>
       </c>
       <c r="R73" t="n">
-        <v>7040287</v>
+        <v>7040466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Naturskog.</t>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10042,10 +10042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131889810</v>
+        <v>131889785</v>
       </c>
       <c r="B74" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10053,29 +10053,28 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -10085,10 +10084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>497721</v>
+        <v>497617</v>
       </c>
       <c r="R74" t="n">
-        <v>7040314</v>
+        <v>7040562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -10123,17 +10122,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10149,22 +10144,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10182,10 +10172,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131889783</v>
+        <v>131889534</v>
       </c>
       <c r="B75" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10224,10 +10214,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>497799</v>
+        <v>497640</v>
       </c>
       <c r="R75" t="n">
-        <v>7040466</v>
+        <v>7040232</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10277,11 +10267,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ75" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10292,14 +10277,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10317,32 +10297,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131889785</v>
+        <v>131889528</v>
       </c>
       <c r="B76" t="n">
-        <v>91846</v>
+        <v>91811</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10359,10 +10339,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>497617</v>
+        <v>497610</v>
       </c>
       <c r="R76" t="n">
-        <v>7040562</v>
+        <v>7040287</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10414,22 +10394,27 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
+          <t>Naturskog.</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>ullticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10447,10 +10432,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131889534</v>
+        <v>131889810</v>
       </c>
       <c r="B77" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10458,28 +10443,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -10489,10 +10475,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>497640</v>
+        <v>497721</v>
       </c>
       <c r="R77" t="n">
-        <v>7040232</v>
+        <v>7040314</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10527,13 +10513,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10542,6 +10532,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
       <c r="AJ77" t="inlineStr">
         <is>
           <t>gran</t>
@@ -10552,9 +10547,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10575,7 +10575,7 @@
         <v>131889869</v>
       </c>
       <c r="B78" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>131889863</v>
       </c>
       <c r="B79" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>131889831</v>
       </c>
       <c r="B80" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>131889838</v>
       </c>
       <c r="B81" t="n">
-        <v>91860</v>
+        <v>91862</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>131889847</v>
       </c>
       <c r="B82" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>131889789</v>
       </c>
       <c r="B83" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>131889866</v>
       </c>
       <c r="B84" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>131889540</v>
       </c>
       <c r="B85" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>131889880</v>
       </c>
       <c r="B86" t="n">
-        <v>89231</v>
+        <v>89233</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>131889532</v>
       </c>
       <c r="B87" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>131889868</v>
       </c>
       <c r="B88" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>131889795</v>
       </c>
       <c r="B89" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>131889811</v>
       </c>
       <c r="B90" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>131889815</v>
       </c>
       <c r="B91" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>131889818</v>
       </c>
       <c r="B92" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12540,61 +12540,52 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131889823</v>
+        <v>131889835</v>
       </c>
       <c r="B93" t="n">
-        <v>57753</v>
+        <v>91844</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102621</v>
+        <v>1108</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497598</v>
+        <v>497549</v>
       </c>
       <c r="R93" t="n">
-        <v>7040321</v>
+        <v>7040130</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12635,6 +12626,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -12646,6 +12638,21 @@
       <c r="AI93" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12663,10 +12670,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131889835</v>
+        <v>131889533</v>
       </c>
       <c r="B94" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12674,21 +12681,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -12705,10 +12712,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497549</v>
+        <v>497784</v>
       </c>
       <c r="R94" t="n">
-        <v>7040130</v>
+        <v>7040452</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12758,11 +12765,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
-        </is>
-      </c>
       <c r="AJ94" t="inlineStr">
         <is>
           <t>gran</t>
@@ -12773,9 +12775,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -12793,52 +12800,61 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131889533</v>
+        <v>131889823</v>
       </c>
       <c r="B95" t="n">
-        <v>91846</v>
+        <v>57755</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>102621</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Naturskog vid Hällgrensflon och Rismyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>497784</v>
+        <v>497598</v>
       </c>
       <c r="R95" t="n">
-        <v>7040452</v>
+        <v>7040321</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12879,7 +12895,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12888,24 +12903,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
         <v>131889786</v>
       </c>
       <c r="B96" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>131889853</v>
       </c>
       <c r="B97" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13179,10 +13179,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131889542</v>
+        <v>131889881</v>
       </c>
       <c r="B98" t="n">
-        <v>78286</v>
+        <v>83248</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13190,21 +13190,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -13217,10 +13217,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497686</v>
+        <v>497527</v>
       </c>
       <c r="R98" t="n">
-        <v>7040411</v>
+        <v>7040360</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13270,19 +13270,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13300,10 +13290,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131889881</v>
+        <v>131889852</v>
       </c>
       <c r="B99" t="n">
-        <v>83246</v>
+        <v>91868</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13311,26 +13301,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -13338,10 +13328,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497527</v>
+        <v>497574</v>
       </c>
       <c r="R99" t="n">
-        <v>7040360</v>
+        <v>7040148</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13394,6 +13384,21 @@
       <c r="AI99" t="inlineStr">
         <is>
           <t>Naturskog (enligt Länsstyrelsen).</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13411,10 +13416,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131889852</v>
+        <v>131889542</v>
       </c>
       <c r="B100" t="n">
-        <v>91866</v>
+        <v>78288</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13422,26 +13427,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13449,10 +13454,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497574</v>
+        <v>497686</v>
       </c>
       <c r="R100" t="n">
-        <v>7040148</v>
+        <v>7040411</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13500,11 +13505,6 @@
       <c r="AH100" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -13540,7 +13540,7 @@
         <v>131889805</v>
       </c>
       <c r="B101" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>131889806</v>
       </c>
       <c r="B102" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>131889819</v>
       </c>
       <c r="B103" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>131889817</v>
       </c>
       <c r="B104" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>131889827</v>
       </c>
       <c r="B105" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>131889777</v>
       </c>
       <c r="B106" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>131889525</v>
       </c>
       <c r="B107" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>131889527</v>
       </c>
       <c r="B108" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>131889864</v>
       </c>
       <c r="B109" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14723,32 +14723,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131889797</v>
+        <v>131889784</v>
       </c>
       <c r="B110" t="n">
-        <v>92569</v>
+        <v>91848</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -14765,10 +14765,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>497512</v>
+        <v>497693</v>
       </c>
       <c r="R110" t="n">
-        <v>7040344</v>
+        <v>7040594</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14816,6 +14816,11 @@
       <c r="AH110" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -14848,40 +14853,39 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131889813</v>
+        <v>131889828</v>
       </c>
       <c r="B111" t="n">
-        <v>57912</v>
+        <v>92231</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
@@ -14891,10 +14895,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>497538</v>
+        <v>497800</v>
       </c>
       <c r="R111" t="n">
-        <v>7040327</v>
+        <v>7040458</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14929,17 +14933,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -14983,10 +14983,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131889784</v>
+        <v>131889859</v>
       </c>
       <c r="B112" t="n">
-        <v>91846</v>
+        <v>79276</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14994,30 +14994,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -15025,10 +15029,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>497693</v>
+        <v>497784</v>
       </c>
       <c r="R112" t="n">
-        <v>7040594</v>
+        <v>7040497</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -15063,6 +15067,11 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt!! Flera särskilt långväxta bålar där en är över 70 cm lång.</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -15076,11 +15085,6 @@
       <c r="AH112" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -15113,32 +15117,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131889828</v>
+        <v>131889797</v>
       </c>
       <c r="B113" t="n">
-        <v>92229</v>
+        <v>92571</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1506</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -15155,10 +15159,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>497800</v>
+        <v>497512</v>
       </c>
       <c r="R113" t="n">
-        <v>7040458</v>
+        <v>7040344</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -15206,11 +15210,6 @@
       <c r="AH113" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -15246,7 +15245,7 @@
         <v>131889778</v>
       </c>
       <c r="B114" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -15369,10 +15368,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131889859</v>
+        <v>131889813</v>
       </c>
       <c r="B115" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15380,34 +15379,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -15415,10 +15411,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>497784</v>
+        <v>497538</v>
       </c>
       <c r="R115" t="n">
-        <v>7040497</v>
+        <v>7040327</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15455,7 +15451,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt!! Flera särskilt långväxta bålar där en är över 70 cm lång.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15464,13 +15460,17 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>Naturskog (enligt Länsstyrelsen).</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -15503,10 +15503,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131889814</v>
+        <v>131889839</v>
       </c>
       <c r="B116" t="n">
-        <v>57912</v>
+        <v>91862</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15514,29 +15514,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -15546,10 +15545,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>497490</v>
+        <v>497618</v>
       </c>
       <c r="R116" t="n">
-        <v>7040364</v>
+        <v>7040361</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15584,17 +15583,13 @@
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -15638,10 +15633,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131889839</v>
+        <v>131889814</v>
       </c>
       <c r="B117" t="n">
-        <v>91860</v>
+        <v>57914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15649,28 +15644,29 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
@@ -15680,10 +15676,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>497618</v>
+        <v>497490</v>
       </c>
       <c r="R117" t="n">
-        <v>7040361</v>
+        <v>7040364</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15718,13 +15714,17 @@
           <t>2026-03-21</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -15771,7 +15771,7 @@
         <v>131889836</v>
       </c>
       <c r="B118" t="n">
-        <v>91842</v>
+        <v>91844</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>131889882</v>
       </c>
       <c r="B119" t="n">
-        <v>83246</v>
+        <v>83248</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>131889850</v>
       </c>
       <c r="B120" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>131889856</v>
       </c>
       <c r="B121" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>131889812</v>
       </c>
       <c r="B122" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>131889821</v>
       </c>
       <c r="B123" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
